--- a/docs/CHECK LIST - frente de serviço MAIO.xlsx
+++ b/docs/CHECK LIST - frente de serviço MAIO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A165575-2011-4410-AE44-DBF7E5E1D7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA0E438-DDBC-4182-B69C-E89CEB37390F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="263">
   <si>
     <t>DATA </t>
   </si>
@@ -141,9 +141,6 @@
     <t>PGR ;PAE;PLANO DE ABASTECIMENTO DE VEICULOS ;PGRS;MANUAL KIT MITIGAÇÃO ;</t>
   </si>
   <si>
-    <t>Cesar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Conceição </t>
   </si>
   <si>
@@ -354,9 +351,6 @@
     <t>CORDÃO ABSORVENTE ;MANTA ABSORVENTE ;TRAVESSEIRO ABSORVENTE ;PÁ PLASTICA;TURFA ;</t>
   </si>
   <si>
-    <t xml:space="preserve">Jonathan </t>
-  </si>
-  <si>
     <t>PRECISANDO DE MANUTENÇÃO;Sem dispenser de sabão ;</t>
   </si>
   <si>
@@ -598,21 +592,6 @@
   </si>
   <si>
     <t>PAE;PGRS;PLANO DE ABASTECIMENTO DE VEICULOS ;PGR ;CAROMETRO ATUALIZADO;MANUAL KIT MITIGAÇÃO ;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT São Lucas </t>
-  </si>
-  <si>
-    <t>FALTANDO ITENS ;Falta: máscara ;</t>
-  </si>
-  <si>
-    <t>LUVA;OCULOS;MANTA ABSORVENTE ;PÁ PLASTICA;SACO PARA RESIDUOS CONTAMINADOS;CORDÃO ABSORVENTE ;TRAVESSEIRO ABSORVENTE ;TURFA ;FALTA: MÁSCARA ;</t>
-  </si>
-  <si>
-    <t>FDS PRODUTO HDD - MK DL 20;FDS PRODUTO HDD - MK GOMA MG 25 ;FDS PRODUTO HDD - MKGELAL 4500;FDS GASOLINA;FDS CIMENTO ;FALTA A FDS DO SABÃO ;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jhonatan </t>
   </si>
   <si>
     <t xml:space="preserve">CT BARÃO DE ARARIBA </t>
@@ -977,8 +956,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AA66" totalsRowShown="0">
-  <autoFilter ref="A1:AA66" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AA65" totalsRowShown="0">
+  <autoFilter ref="A1:AA65" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="27">
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="DATA " dataDxfId="26"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="EQUIPE " dataDxfId="25"/>
@@ -1309,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA66"/>
+  <dimension ref="A1:AA65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="27" width="20" bestFit="1" customWidth="1"/>
@@ -1459,49 +1438,49 @@
         <v>46118</v>
       </c>
       <c r="B3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D3" t="s">
         <v>38</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" t="s">
         <v>40</v>
       </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3" t="s">
-        <v>34</v>
-      </c>
-      <c r="T3" t="s">
-        <v>34</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>41</v>
-      </c>
-      <c r="V3" t="s">
-        <v>42</v>
       </c>
       <c r="W3" t="s">
         <v>36</v>
@@ -1510,7 +1489,7 @@
         <v>37</v>
       </c>
       <c r="Y3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
@@ -1518,37 +1497,37 @@
         <v>46118</v>
       </c>
       <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
         <v>44</v>
       </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" t="s">
         <v>45</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>46</v>
       </c>
       <c r="R4" t="s">
         <v>34</v>
@@ -1563,13 +1542,13 @@
         <v>31</v>
       </c>
       <c r="W4" t="s">
+        <v>46</v>
+      </c>
+      <c r="X4" t="s">
         <v>47</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>48</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
@@ -1577,55 +1556,55 @@
         <v>46118</v>
       </c>
       <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>45</v>
+      </c>
+      <c r="R5" t="s">
+        <v>34</v>
+      </c>
+      <c r="T5" t="s">
+        <v>34</v>
+      </c>
+      <c r="V5" t="s">
+        <v>31</v>
+      </c>
+      <c r="W5" t="s">
+        <v>46</v>
+      </c>
+      <c r="X5" t="s">
         <v>50</v>
       </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" t="s">
-        <v>32</v>
-      </c>
-      <c r="P5" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>46</v>
-      </c>
-      <c r="R5" t="s">
-        <v>34</v>
-      </c>
-      <c r="T5" t="s">
-        <v>34</v>
-      </c>
-      <c r="V5" t="s">
-        <v>31</v>
-      </c>
-      <c r="W5" t="s">
-        <v>47</v>
-      </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>51</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
@@ -1633,61 +1612,61 @@
         <v>46119</v>
       </c>
       <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" t="s">
         <v>53</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" t="s">
         <v>54</v>
       </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" t="s">
-        <v>32</v>
-      </c>
-      <c r="N6" t="s">
-        <v>34</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>34</v>
+      </c>
+      <c r="R6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S6" t="s">
         <v>55</v>
       </c>
-      <c r="P6" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>34</v>
-      </c>
-      <c r="R6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
+        <v>34</v>
+      </c>
+      <c r="V6" t="s">
+        <v>31</v>
+      </c>
+      <c r="W6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X6" t="s">
         <v>56</v>
       </c>
-      <c r="T6" t="s">
-        <v>34</v>
-      </c>
-      <c r="V6" t="s">
-        <v>31</v>
-      </c>
-      <c r="W6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>57</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
@@ -1695,58 +1674,58 @@
         <v>46119</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>34</v>
+      </c>
+      <c r="S7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T7" t="s">
+        <v>34</v>
+      </c>
+      <c r="U7" t="s">
         <v>59</v>
       </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" t="s">
-        <v>34</v>
-      </c>
-      <c r="P7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>34</v>
-      </c>
-      <c r="S7" t="s">
-        <v>56</v>
-      </c>
-      <c r="T7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
+        <v>31</v>
+      </c>
+      <c r="W7" t="s">
         <v>60</v>
       </c>
-      <c r="V7" t="s">
-        <v>31</v>
-      </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
         <v>61</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
         <v>62</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
@@ -1754,10 +1733,10 @@
         <v>46119</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>
@@ -1775,7 +1754,7 @@
         <v>32</v>
       </c>
       <c r="L8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N8" t="s">
         <v>34</v>
@@ -1793,22 +1772,22 @@
         <v>34</v>
       </c>
       <c r="S8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T8" t="s">
         <v>34</v>
       </c>
       <c r="U8" t="s">
+        <v>64</v>
+      </c>
+      <c r="W8" t="s">
+        <v>46</v>
+      </c>
+      <c r="X8" t="s">
         <v>65</v>
       </c>
-      <c r="W8" t="s">
-        <v>47</v>
-      </c>
-      <c r="X8" t="s">
-        <v>66</v>
-      </c>
       <c r="Y8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
@@ -1816,61 +1795,61 @@
         <v>46119</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>204</v>
       </c>
       <c r="D9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" t="s">
+        <v>34</v>
+      </c>
+      <c r="O9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>34</v>
+      </c>
+      <c r="R9" t="s">
+        <v>34</v>
+      </c>
+      <c r="S9" t="s">
         <v>67</v>
       </c>
-      <c r="E9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" t="s">
-        <v>34</v>
-      </c>
-      <c r="O9" t="s">
-        <v>32</v>
-      </c>
-      <c r="P9" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>34</v>
-      </c>
-      <c r="R9" t="s">
-        <v>34</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
+        <v>34</v>
+      </c>
+      <c r="V9" t="s">
+        <v>31</v>
+      </c>
+      <c r="W9" t="s">
         <v>68</v>
       </c>
-      <c r="T9" t="s">
-        <v>34</v>
-      </c>
-      <c r="V9" t="s">
-        <v>31</v>
-      </c>
-      <c r="W9" t="s">
+      <c r="X9" t="s">
         <v>69</v>
       </c>
-      <c r="X9" t="s">
+      <c r="Y9" t="s">
         <v>70</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
@@ -1878,61 +1857,61 @@
         <v>46120</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>34</v>
+      </c>
+      <c r="R10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S10" t="s">
         <v>72</v>
       </c>
-      <c r="H10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" t="s">
-        <v>40</v>
-      </c>
-      <c r="N10" t="s">
-        <v>34</v>
-      </c>
-      <c r="O10" t="s">
-        <v>32</v>
-      </c>
-      <c r="P10" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>34</v>
-      </c>
-      <c r="R10" t="s">
-        <v>34</v>
-      </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
+        <v>34</v>
+      </c>
+      <c r="V10" t="s">
+        <v>31</v>
+      </c>
+      <c r="W10" t="s">
         <v>73</v>
       </c>
-      <c r="T10" t="s">
-        <v>34</v>
-      </c>
-      <c r="V10" t="s">
-        <v>31</v>
-      </c>
-      <c r="W10" t="s">
+      <c r="X10" t="s">
         <v>74</v>
       </c>
-      <c r="X10" t="s">
-        <v>75</v>
-      </c>
       <c r="Y10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
@@ -1940,61 +1919,61 @@
         <v>46121</v>
       </c>
       <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
         <v>76</v>
       </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>45</v>
+      </c>
+      <c r="R11" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" t="s">
+        <v>67</v>
+      </c>
+      <c r="T11" t="s">
         <v>77</v>
       </c>
-      <c r="H11" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" t="s">
-        <v>32</v>
-      </c>
-      <c r="N11" t="s">
-        <v>34</v>
-      </c>
-      <c r="O11" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>46</v>
-      </c>
-      <c r="R11" t="s">
-        <v>34</v>
-      </c>
-      <c r="S11" t="s">
-        <v>68</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="V11" t="s">
+        <v>31</v>
+      </c>
+      <c r="W11" t="s">
         <v>78</v>
       </c>
-      <c r="V11" t="s">
-        <v>31</v>
-      </c>
-      <c r="W11" t="s">
+      <c r="X11" t="s">
         <v>79</v>
       </c>
-      <c r="X11" t="s">
-        <v>80</v>
-      </c>
       <c r="Y11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
@@ -2002,61 +1981,61 @@
         <v>46120</v>
       </c>
       <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>45</v>
+      </c>
+      <c r="R12" t="s">
+        <v>34</v>
+      </c>
+      <c r="S12" t="s">
+        <v>67</v>
+      </c>
+      <c r="T12" t="s">
+        <v>34</v>
+      </c>
+      <c r="U12" t="s">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" t="s">
-        <v>32</v>
-      </c>
-      <c r="N12" t="s">
-        <v>34</v>
-      </c>
-      <c r="O12" t="s">
-        <v>32</v>
-      </c>
-      <c r="P12" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>46</v>
-      </c>
-      <c r="R12" t="s">
-        <v>34</v>
-      </c>
-      <c r="S12" t="s">
-        <v>68</v>
-      </c>
-      <c r="T12" t="s">
-        <v>34</v>
-      </c>
-      <c r="U12" t="s">
+      <c r="V12" t="s">
+        <v>31</v>
+      </c>
+      <c r="W12" t="s">
         <v>82</v>
       </c>
-      <c r="V12" t="s">
-        <v>31</v>
-      </c>
-      <c r="W12" t="s">
+      <c r="X12" t="s">
         <v>83</v>
       </c>
-      <c r="X12" t="s">
-        <v>84</v>
-      </c>
       <c r="Y12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
@@ -2064,32 +2043,32 @@
         <v>46120</v>
       </c>
       <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" t="s">
         <v>85</v>
       </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" t="s">
-        <v>32</v>
-      </c>
-      <c r="N13" t="s">
-        <v>86</v>
-      </c>
       <c r="O13" t="s">
         <v>32</v>
       </c>
@@ -2097,13 +2076,13 @@
         <v>32</v>
       </c>
       <c r="Q13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R13" t="s">
         <v>34</v>
       </c>
       <c r="S13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T13" t="s">
         <v>34</v>
@@ -2112,13 +2091,13 @@
         <v>31</v>
       </c>
       <c r="W13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X13" t="s">
         <v>69</v>
       </c>
-      <c r="X13" t="s">
+      <c r="Y13" t="s">
         <v>70</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
@@ -2126,61 +2105,61 @@
         <v>46119</v>
       </c>
       <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
         <v>87</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" t="s">
+        <v>34</v>
+      </c>
+      <c r="O14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>45</v>
+      </c>
+      <c r="R14" t="s">
+        <v>34</v>
+      </c>
+      <c r="S14" t="s">
+        <v>55</v>
+      </c>
+      <c r="T14" t="s">
+        <v>34</v>
+      </c>
+      <c r="V14" t="s">
+        <v>31</v>
+      </c>
+      <c r="W14" t="s">
+        <v>68</v>
+      </c>
+      <c r="X14" t="s">
         <v>88</v>
       </c>
-      <c r="E14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" t="s">
-        <v>32</v>
-      </c>
-      <c r="N14" t="s">
-        <v>34</v>
-      </c>
-      <c r="O14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P14" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>46</v>
-      </c>
-      <c r="R14" t="s">
-        <v>34</v>
-      </c>
-      <c r="S14" t="s">
-        <v>56</v>
-      </c>
-      <c r="T14" t="s">
-        <v>34</v>
-      </c>
-      <c r="V14" t="s">
-        <v>31</v>
-      </c>
-      <c r="W14" t="s">
-        <v>69</v>
-      </c>
-      <c r="X14" t="s">
-        <v>89</v>
-      </c>
       <c r="Y14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
@@ -2188,61 +2167,61 @@
         <v>46122</v>
       </c>
       <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" t="s">
+        <v>34</v>
+      </c>
+      <c r="O15" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>34</v>
+      </c>
+      <c r="R15" t="s">
+        <v>34</v>
+      </c>
+      <c r="S15" t="s">
+        <v>55</v>
+      </c>
+      <c r="T15" t="s">
+        <v>34</v>
+      </c>
+      <c r="V15" t="s">
+        <v>31</v>
+      </c>
+      <c r="W15" t="s">
         <v>90</v>
       </c>
-      <c r="D15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" t="s">
-        <v>34</v>
-      </c>
-      <c r="O15" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>34</v>
-      </c>
-      <c r="R15" t="s">
-        <v>34</v>
-      </c>
-      <c r="S15" t="s">
-        <v>56</v>
-      </c>
-      <c r="T15" t="s">
-        <v>34</v>
-      </c>
-      <c r="V15" t="s">
-        <v>31</v>
-      </c>
-      <c r="W15" t="s">
+      <c r="X15" t="s">
         <v>91</v>
       </c>
-      <c r="X15" t="s">
-        <v>92</v>
-      </c>
       <c r="Y15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
@@ -2250,10 +2229,10 @@
         <v>46122</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -2283,31 +2262,31 @@
         <v>32</v>
       </c>
       <c r="Q16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R16" t="s">
         <v>34</v>
       </c>
       <c r="S16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T16" t="s">
         <v>34</v>
       </c>
       <c r="U16" t="s">
+        <v>92</v>
+      </c>
+      <c r="V16" t="s">
+        <v>31</v>
+      </c>
+      <c r="W16" t="s">
         <v>93</v>
       </c>
-      <c r="V16" t="s">
-        <v>31</v>
-      </c>
-      <c r="W16" t="s">
-        <v>94</v>
-      </c>
       <c r="X16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -2315,10 +2294,10 @@
         <v>46122</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s">
         <v>31</v>
@@ -2339,34 +2318,34 @@
         <v>32</v>
       </c>
       <c r="N17" t="s">
+        <v>94</v>
+      </c>
+      <c r="O17" t="s">
+        <v>32</v>
+      </c>
+      <c r="P17" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" t="s">
+        <v>34</v>
+      </c>
+      <c r="S17" t="s">
+        <v>67</v>
+      </c>
+      <c r="T17" t="s">
+        <v>34</v>
+      </c>
+      <c r="V17" t="s">
+        <v>31</v>
+      </c>
+      <c r="W17" t="s">
         <v>95</v>
       </c>
-      <c r="O17" t="s">
-        <v>32</v>
-      </c>
-      <c r="P17" t="s">
-        <v>32</v>
-      </c>
-      <c r="R17" t="s">
-        <v>34</v>
-      </c>
-      <c r="S17" t="s">
-        <v>68</v>
-      </c>
-      <c r="T17" t="s">
-        <v>34</v>
-      </c>
-      <c r="V17" t="s">
-        <v>31</v>
-      </c>
-      <c r="W17" t="s">
+      <c r="X17" t="s">
         <v>96</v>
       </c>
-      <c r="X17" t="s">
-        <v>97</v>
-      </c>
       <c r="Y17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
@@ -2374,61 +2353,61 @@
         <v>46125</v>
       </c>
       <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" t="s">
+        <v>39</v>
+      </c>
+      <c r="N18" t="s">
+        <v>34</v>
+      </c>
+      <c r="O18" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>45</v>
+      </c>
+      <c r="R18" t="s">
+        <v>45</v>
+      </c>
+      <c r="S18" t="s">
+        <v>55</v>
+      </c>
+      <c r="T18" t="s">
+        <v>34</v>
+      </c>
+      <c r="V18" t="s">
+        <v>31</v>
+      </c>
+      <c r="W18" t="s">
         <v>98</v>
       </c>
-      <c r="D18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" t="s">
-        <v>40</v>
-      </c>
-      <c r="N18" t="s">
-        <v>34</v>
-      </c>
-      <c r="O18" t="s">
-        <v>32</v>
-      </c>
-      <c r="P18" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>46</v>
-      </c>
-      <c r="R18" t="s">
-        <v>46</v>
-      </c>
-      <c r="S18" t="s">
-        <v>56</v>
-      </c>
-      <c r="T18" t="s">
-        <v>34</v>
-      </c>
-      <c r="V18" t="s">
-        <v>31</v>
-      </c>
-      <c r="W18" t="s">
+      <c r="X18" t="s">
         <v>99</v>
       </c>
-      <c r="X18" t="s">
-        <v>100</v>
-      </c>
       <c r="Y18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
@@ -2436,49 +2415,49 @@
         <v>46126</v>
       </c>
       <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" t="s">
         <v>101</v>
       </c>
-      <c r="D19" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" t="s">
-        <v>32</v>
-      </c>
-      <c r="L19" t="s">
-        <v>32</v>
-      </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>34</v>
+      </c>
+      <c r="R19" t="s">
+        <v>34</v>
+      </c>
+      <c r="T19" t="s">
+        <v>34</v>
+      </c>
+      <c r="W19" t="s">
         <v>102</v>
       </c>
-      <c r="O19" t="s">
-        <v>32</v>
-      </c>
-      <c r="P19" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>34</v>
-      </c>
-      <c r="R19" t="s">
-        <v>34</v>
-      </c>
-      <c r="T19" t="s">
-        <v>34</v>
-      </c>
-      <c r="W19" t="s">
+      <c r="X19" t="s">
         <v>103</v>
-      </c>
-      <c r="X19" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -2486,55 +2465,55 @@
         <v>46126</v>
       </c>
       <c r="B20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" t="s">
         <v>105</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" t="s">
+        <v>34</v>
+      </c>
+      <c r="O20" t="s">
+        <v>32</v>
+      </c>
+      <c r="P20" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>34</v>
+      </c>
+      <c r="R20" t="s">
+        <v>34</v>
+      </c>
+      <c r="T20" t="s">
+        <v>34</v>
+      </c>
+      <c r="W20" t="s">
+        <v>46</v>
+      </c>
+      <c r="X20" t="s">
         <v>106</v>
       </c>
-      <c r="E20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" t="s">
-        <v>32</v>
-      </c>
-      <c r="K20" t="s">
-        <v>32</v>
-      </c>
-      <c r="L20" t="s">
-        <v>32</v>
-      </c>
-      <c r="N20" t="s">
-        <v>34</v>
-      </c>
-      <c r="O20" t="s">
-        <v>32</v>
-      </c>
-      <c r="P20" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>34</v>
-      </c>
-      <c r="R20" t="s">
-        <v>34</v>
-      </c>
-      <c r="T20" t="s">
-        <v>34</v>
-      </c>
-      <c r="W20" t="s">
-        <v>47</v>
-      </c>
-      <c r="X20" t="s">
-        <v>107</v>
-      </c>
       <c r="Y20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
@@ -2542,10 +2521,10 @@
         <v>46135</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s">
         <v>31</v>
@@ -2578,22 +2557,22 @@
         <v>34</v>
       </c>
       <c r="S21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T21" t="s">
         <v>34</v>
       </c>
       <c r="U21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="W21" t="s">
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
@@ -2601,61 +2580,61 @@
         <v>46135</v>
       </c>
       <c r="B22" t="s">
+        <v>204</v>
+      </c>
+      <c r="D22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" t="s">
+        <v>108</v>
+      </c>
+      <c r="O22" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>34</v>
+      </c>
+      <c r="R22" t="s">
+        <v>34</v>
+      </c>
+      <c r="S22" t="s">
+        <v>67</v>
+      </c>
+      <c r="T22" t="s">
+        <v>34</v>
+      </c>
+      <c r="V22" t="s">
+        <v>31</v>
+      </c>
+      <c r="W22" t="s">
         <v>109</v>
       </c>
-      <c r="D22" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" t="s">
-        <v>32</v>
-      </c>
-      <c r="K22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L22" t="s">
-        <v>32</v>
-      </c>
-      <c r="N22" t="s">
+      <c r="X22" t="s">
         <v>110</v>
       </c>
-      <c r="O22" t="s">
-        <v>32</v>
-      </c>
-      <c r="P22" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>34</v>
-      </c>
-      <c r="R22" t="s">
-        <v>34</v>
-      </c>
-      <c r="S22" t="s">
-        <v>68</v>
-      </c>
-      <c r="T22" t="s">
-        <v>34</v>
-      </c>
-      <c r="V22" t="s">
-        <v>31</v>
-      </c>
-      <c r="W22" t="s">
-        <v>111</v>
-      </c>
-      <c r="X22" t="s">
-        <v>112</v>
-      </c>
       <c r="Y22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
@@ -2663,11 +2642,11 @@
         <v>46135</v>
       </c>
       <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" t="s">
         <v>53</v>
       </c>
-      <c r="D23" t="s">
-        <v>54</v>
-      </c>
       <c r="E23" t="s">
         <v>31</v>
       </c>
@@ -2702,19 +2681,19 @@
         <v>34</v>
       </c>
       <c r="S23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T23" t="s">
         <v>34</v>
       </c>
       <c r="W23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="X23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
@@ -2722,52 +2701,52 @@
         <v>46135</v>
       </c>
       <c r="B24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" t="s">
+        <v>39</v>
+      </c>
+      <c r="N24" t="s">
+        <v>113</v>
+      </c>
+      <c r="O24" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>34</v>
+      </c>
+      <c r="S24" t="s">
+        <v>55</v>
+      </c>
+      <c r="T24" t="s">
+        <v>34</v>
+      </c>
+      <c r="W24" t="s">
         <v>114</v>
       </c>
-      <c r="D24" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" t="s">
-        <v>32</v>
-      </c>
-      <c r="J24" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L24" t="s">
-        <v>40</v>
-      </c>
-      <c r="N24" t="s">
+      <c r="X24" t="s">
         <v>115</v>
       </c>
-      <c r="O24" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>34</v>
-      </c>
-      <c r="S24" t="s">
-        <v>56</v>
-      </c>
-      <c r="T24" t="s">
-        <v>34</v>
-      </c>
-      <c r="W24" t="s">
-        <v>116</v>
-      </c>
-      <c r="X24" t="s">
-        <v>117</v>
-      </c>
       <c r="Y24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
@@ -2775,10 +2754,10 @@
         <v>46135</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s">
         <v>31</v>
@@ -2799,7 +2778,7 @@
         <v>32</v>
       </c>
       <c r="N25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="O25" t="s">
         <v>32</v>
@@ -2814,7 +2793,7 @@
         <v>34</v>
       </c>
       <c r="S25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T25" t="s">
         <v>34</v>
@@ -2823,13 +2802,13 @@
         <v>31</v>
       </c>
       <c r="W25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="X25" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Y25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
@@ -2837,61 +2816,61 @@
         <v>46139</v>
       </c>
       <c r="B26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" t="s">
+        <v>32</v>
+      </c>
+      <c r="N26" t="s">
+        <v>34</v>
+      </c>
+      <c r="P26" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>34</v>
+      </c>
+      <c r="R26" t="s">
+        <v>34</v>
+      </c>
+      <c r="S26" t="s">
         <v>120</v>
       </c>
-      <c r="D26" t="s">
+      <c r="T26" t="s">
+        <v>34</v>
+      </c>
+      <c r="U26" t="s">
         <v>121</v>
       </c>
-      <c r="E26" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" t="s">
-        <v>40</v>
-      </c>
-      <c r="J26" t="s">
-        <v>32</v>
-      </c>
-      <c r="K26" t="s">
-        <v>32</v>
-      </c>
-      <c r="L26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N26" t="s">
-        <v>34</v>
-      </c>
-      <c r="P26" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>34</v>
-      </c>
-      <c r="R26" t="s">
-        <v>34</v>
-      </c>
-      <c r="S26" t="s">
+      <c r="V26" t="s">
+        <v>31</v>
+      </c>
+      <c r="W26" t="s">
         <v>122</v>
       </c>
-      <c r="T26" t="s">
-        <v>34</v>
-      </c>
-      <c r="U26" t="s">
+      <c r="X26" t="s">
         <v>123</v>
       </c>
-      <c r="V26" t="s">
-        <v>31</v>
-      </c>
-      <c r="W26" t="s">
-        <v>124</v>
-      </c>
-      <c r="X26" t="s">
-        <v>125</v>
-      </c>
       <c r="Y26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
@@ -2899,64 +2878,64 @@
         <v>46139</v>
       </c>
       <c r="B27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" t="s">
+        <v>32</v>
+      </c>
+      <c r="N27" t="s">
+        <v>94</v>
+      </c>
+      <c r="O27" t="s">
+        <v>32</v>
+      </c>
+      <c r="P27" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>34</v>
+      </c>
+      <c r="R27" t="s">
+        <v>34</v>
+      </c>
+      <c r="S27" t="s">
+        <v>125</v>
+      </c>
+      <c r="T27" t="s">
         <v>126</v>
       </c>
-      <c r="D27" t="s">
-        <v>121</v>
-      </c>
-      <c r="E27" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" t="s">
-        <v>40</v>
-      </c>
-      <c r="J27" t="s">
-        <v>32</v>
-      </c>
-      <c r="K27" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" t="s">
-        <v>32</v>
-      </c>
-      <c r="N27" t="s">
-        <v>95</v>
-      </c>
-      <c r="O27" t="s">
-        <v>32</v>
-      </c>
-      <c r="P27" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>34</v>
-      </c>
-      <c r="R27" t="s">
-        <v>34</v>
-      </c>
-      <c r="S27" t="s">
+      <c r="U27" t="s">
         <v>127</v>
       </c>
-      <c r="T27" t="s">
-        <v>128</v>
-      </c>
-      <c r="U27" t="s">
-        <v>129</v>
-      </c>
       <c r="V27" t="s">
         <v>31</v>
       </c>
       <c r="W27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="X27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Y27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
@@ -2964,61 +2943,61 @@
         <v>46139</v>
       </c>
       <c r="B28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" t="s">
+        <v>34</v>
+      </c>
+      <c r="O28" t="s">
+        <v>32</v>
+      </c>
+      <c r="P28" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>34</v>
+      </c>
+      <c r="R28" t="s">
+        <v>34</v>
+      </c>
+      <c r="S28" t="s">
+        <v>125</v>
+      </c>
+      <c r="T28" t="s">
+        <v>129</v>
+      </c>
+      <c r="U28" t="s">
         <v>130</v>
       </c>
-      <c r="D28" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" t="s">
-        <v>40</v>
-      </c>
-      <c r="J28" t="s">
-        <v>32</v>
-      </c>
-      <c r="K28" t="s">
-        <v>32</v>
-      </c>
-      <c r="L28" t="s">
-        <v>32</v>
-      </c>
-      <c r="N28" t="s">
-        <v>34</v>
-      </c>
-      <c r="O28" t="s">
-        <v>32</v>
-      </c>
-      <c r="P28" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>34</v>
-      </c>
-      <c r="R28" t="s">
-        <v>34</v>
-      </c>
-      <c r="S28" t="s">
-        <v>127</v>
-      </c>
-      <c r="T28" t="s">
+      <c r="V28" t="s">
+        <v>31</v>
+      </c>
+      <c r="W28" t="s">
         <v>131</v>
       </c>
-      <c r="U28" t="s">
+      <c r="X28" t="s">
         <v>132</v>
       </c>
-      <c r="V28" t="s">
-        <v>31</v>
-      </c>
-      <c r="W28" t="s">
+      <c r="Y28" t="s">
         <v>133</v>
-      </c>
-      <c r="X28" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
@@ -3026,61 +3005,61 @@
         <v>46139</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D29" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" t="s">
+        <v>34</v>
+      </c>
+      <c r="O29" t="s">
+        <v>32</v>
+      </c>
+      <c r="P29" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>34</v>
+      </c>
+      <c r="R29" t="s">
+        <v>34</v>
+      </c>
+      <c r="S29" t="s">
+        <v>135</v>
+      </c>
+      <c r="T29" t="s">
         <v>136</v>
       </c>
-      <c r="E29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" t="s">
-        <v>32</v>
-      </c>
-      <c r="K29" t="s">
-        <v>32</v>
-      </c>
-      <c r="L29" t="s">
-        <v>32</v>
-      </c>
-      <c r="N29" t="s">
-        <v>34</v>
-      </c>
-      <c r="O29" t="s">
-        <v>32</v>
-      </c>
-      <c r="P29" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>34</v>
-      </c>
-      <c r="R29" t="s">
-        <v>34</v>
-      </c>
-      <c r="S29" t="s">
+      <c r="U29" t="s">
         <v>137</v>
       </c>
-      <c r="T29" t="s">
+      <c r="V29" t="s">
+        <v>31</v>
+      </c>
+      <c r="W29" t="s">
         <v>138</v>
       </c>
-      <c r="U29" t="s">
+      <c r="X29" t="s">
         <v>139</v>
       </c>
-      <c r="V29" t="s">
-        <v>31</v>
-      </c>
-      <c r="W29" t="s">
-        <v>140</v>
-      </c>
-      <c r="X29" t="s">
-        <v>141</v>
-      </c>
       <c r="Y29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
@@ -3088,49 +3067,49 @@
         <v>46140</v>
       </c>
       <c r="B30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" t="s">
+        <v>32</v>
+      </c>
+      <c r="N30" t="s">
+        <v>34</v>
+      </c>
+      <c r="O30" t="s">
+        <v>32</v>
+      </c>
+      <c r="U30" t="s">
         <v>142</v>
-      </c>
-      <c r="D30" t="s">
-        <v>143</v>
-      </c>
-      <c r="E30" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" t="s">
-        <v>32</v>
-      </c>
-      <c r="J30" t="s">
-        <v>32</v>
-      </c>
-      <c r="K30" t="s">
-        <v>32</v>
-      </c>
-      <c r="L30" t="s">
-        <v>32</v>
-      </c>
-      <c r="N30" t="s">
-        <v>34</v>
-      </c>
-      <c r="O30" t="s">
-        <v>32</v>
-      </c>
-      <c r="U30" t="s">
-        <v>144</v>
       </c>
       <c r="V30" t="s">
         <v>28</v>
       </c>
       <c r="W30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
@@ -3138,64 +3117,64 @@
         <v>46140</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" t="s">
+        <v>32</v>
+      </c>
+      <c r="K31" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" t="s">
+        <v>32</v>
+      </c>
+      <c r="N31" t="s">
+        <v>34</v>
+      </c>
+      <c r="O31" t="s">
+        <v>32</v>
+      </c>
+      <c r="P31" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>34</v>
+      </c>
+      <c r="R31" t="s">
+        <v>34</v>
+      </c>
+      <c r="S31" t="s">
+        <v>135</v>
+      </c>
+      <c r="T31" t="s">
         <v>143</v>
       </c>
-      <c r="E31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H31" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" t="s">
-        <v>32</v>
-      </c>
-      <c r="J31" t="s">
-        <v>32</v>
-      </c>
-      <c r="K31" t="s">
-        <v>32</v>
-      </c>
-      <c r="L31" t="s">
-        <v>32</v>
-      </c>
-      <c r="N31" t="s">
-        <v>34</v>
-      </c>
-      <c r="O31" t="s">
-        <v>32</v>
-      </c>
-      <c r="P31" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>34</v>
-      </c>
-      <c r="R31" t="s">
-        <v>34</v>
-      </c>
-      <c r="S31" t="s">
-        <v>137</v>
-      </c>
-      <c r="T31" t="s">
+      <c r="U31" t="s">
+        <v>144</v>
+      </c>
+      <c r="V31" t="s">
+        <v>31</v>
+      </c>
+      <c r="W31" t="s">
         <v>145</v>
       </c>
-      <c r="U31" t="s">
-        <v>146</v>
-      </c>
-      <c r="V31" t="s">
-        <v>31</v>
-      </c>
-      <c r="W31" t="s">
-        <v>147</v>
-      </c>
       <c r="X31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
@@ -3203,10 +3182,10 @@
         <v>46140</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E32" t="s">
         <v>31</v>
@@ -3215,7 +3194,7 @@
         <v>32</v>
       </c>
       <c r="I32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J32" t="s">
         <v>32</v>
@@ -3224,7 +3203,7 @@
         <v>32</v>
       </c>
       <c r="L32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N32" t="s">
         <v>34</v>
@@ -3242,25 +3221,25 @@
         <v>34</v>
       </c>
       <c r="S32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="T32" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="U32" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="V32" t="s">
         <v>28</v>
       </c>
       <c r="W32" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="X32" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Y32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
@@ -3268,61 +3247,61 @@
         <v>46142</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" t="s">
+        <v>32</v>
+      </c>
+      <c r="K33" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" t="s">
+        <v>32</v>
+      </c>
+      <c r="N33" t="s">
+        <v>34</v>
+      </c>
+      <c r="O33" t="s">
+        <v>32</v>
+      </c>
+      <c r="P33" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>34</v>
+      </c>
+      <c r="R33" t="s">
+        <v>34</v>
+      </c>
+      <c r="S33" t="s">
+        <v>150</v>
+      </c>
+      <c r="T33" t="s">
+        <v>34</v>
+      </c>
+      <c r="V33" t="s">
+        <v>31</v>
+      </c>
+      <c r="W33" t="s">
         <v>151</v>
       </c>
-      <c r="E33" t="s">
-        <v>31</v>
-      </c>
-      <c r="H33" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" t="s">
-        <v>32</v>
-      </c>
-      <c r="J33" t="s">
-        <v>32</v>
-      </c>
-      <c r="K33" t="s">
-        <v>32</v>
-      </c>
-      <c r="L33" t="s">
-        <v>32</v>
-      </c>
-      <c r="N33" t="s">
-        <v>34</v>
-      </c>
-      <c r="O33" t="s">
-        <v>32</v>
-      </c>
-      <c r="P33" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>34</v>
-      </c>
-      <c r="R33" t="s">
-        <v>34</v>
-      </c>
-      <c r="S33" t="s">
+      <c r="X33" t="s">
         <v>152</v>
       </c>
-      <c r="T33" t="s">
-        <v>34</v>
-      </c>
-      <c r="V33" t="s">
-        <v>31</v>
-      </c>
-      <c r="W33" t="s">
-        <v>153</v>
-      </c>
-      <c r="X33" t="s">
-        <v>154</v>
-      </c>
       <c r="Y33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
@@ -3330,10 +3309,10 @@
         <v>46142</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E34" t="s">
         <v>31</v>
@@ -3363,31 +3342,31 @@
         <v>28</v>
       </c>
       <c r="Q34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R34" t="s">
         <v>34</v>
       </c>
       <c r="S34" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="T34" t="s">
+        <v>153</v>
+      </c>
+      <c r="U34" t="s">
+        <v>154</v>
+      </c>
+      <c r="V34" t="s">
+        <v>31</v>
+      </c>
+      <c r="W34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X34" t="s">
         <v>155</v>
       </c>
-      <c r="U34" t="s">
-        <v>156</v>
-      </c>
-      <c r="V34" t="s">
-        <v>31</v>
-      </c>
-      <c r="W34" t="s">
-        <v>79</v>
-      </c>
-      <c r="X34" t="s">
-        <v>157</v>
-      </c>
       <c r="Y34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
@@ -3395,10 +3374,10 @@
         <v>46142</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D35" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E35" t="s">
         <v>31</v>
@@ -3407,7 +3386,7 @@
         <v>32</v>
       </c>
       <c r="I35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J35" t="s">
         <v>32</v>
@@ -3431,19 +3410,19 @@
         <v>34</v>
       </c>
       <c r="S35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="V35" t="s">
         <v>31</v>
       </c>
       <c r="W35" t="s">
+        <v>156</v>
+      </c>
+      <c r="X35" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y35" t="s">
         <v>158</v>
-      </c>
-      <c r="X35" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
@@ -3451,10 +3430,10 @@
         <v>46142</v>
       </c>
       <c r="B36" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E36" t="s">
         <v>31</v>
@@ -3463,7 +3442,7 @@
         <v>32</v>
       </c>
       <c r="I36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J36" t="s">
         <v>32</v>
@@ -3490,7 +3469,7 @@
         <v>34</v>
       </c>
       <c r="S36" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="V36" t="s">
         <v>31</v>
@@ -3501,64 +3480,64 @@
         <v>46147</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" t="s">
+        <v>39</v>
+      </c>
+      <c r="N37" t="s">
+        <v>34</v>
+      </c>
+      <c r="O37" t="s">
+        <v>32</v>
+      </c>
+      <c r="P37" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>34</v>
+      </c>
+      <c r="R37" t="s">
+        <v>34</v>
+      </c>
+      <c r="S37" t="s">
+        <v>161</v>
+      </c>
+      <c r="T37" t="s">
         <v>162</v>
       </c>
-      <c r="E37" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" t="s">
-        <v>32</v>
-      </c>
-      <c r="J37" t="s">
-        <v>32</v>
-      </c>
-      <c r="K37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L37" t="s">
-        <v>40</v>
-      </c>
-      <c r="N37" t="s">
-        <v>34</v>
-      </c>
-      <c r="O37" t="s">
-        <v>32</v>
-      </c>
-      <c r="P37" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>34</v>
-      </c>
-      <c r="R37" t="s">
-        <v>34</v>
-      </c>
-      <c r="S37" t="s">
+      <c r="U37" t="s">
         <v>163</v>
       </c>
-      <c r="T37" t="s">
-        <v>164</v>
-      </c>
-      <c r="U37" t="s">
-        <v>165</v>
-      </c>
       <c r="V37" t="s">
         <v>31</v>
       </c>
       <c r="W37" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="X37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
@@ -3566,64 +3545,64 @@
         <v>46147</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D38" t="s">
+        <v>164</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" t="s">
+        <v>32</v>
+      </c>
+      <c r="K38" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38" t="s">
+        <v>39</v>
+      </c>
+      <c r="N38" t="s">
+        <v>34</v>
+      </c>
+      <c r="O38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P38" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>34</v>
+      </c>
+      <c r="R38" t="s">
+        <v>34</v>
+      </c>
+      <c r="S38" t="s">
+        <v>161</v>
+      </c>
+      <c r="T38" t="s">
+        <v>126</v>
+      </c>
+      <c r="U38" t="s">
+        <v>165</v>
+      </c>
+      <c r="V38" t="s">
+        <v>31</v>
+      </c>
+      <c r="W38" t="s">
         <v>166</v>
       </c>
-      <c r="E38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H38" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" t="s">
-        <v>40</v>
-      </c>
-      <c r="J38" t="s">
-        <v>32</v>
-      </c>
-      <c r="K38" t="s">
-        <v>32</v>
-      </c>
-      <c r="L38" t="s">
-        <v>40</v>
-      </c>
-      <c r="N38" t="s">
-        <v>34</v>
-      </c>
-      <c r="O38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P38" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>34</v>
-      </c>
-      <c r="R38" t="s">
-        <v>34</v>
-      </c>
-      <c r="S38" t="s">
-        <v>163</v>
-      </c>
-      <c r="T38" t="s">
-        <v>128</v>
-      </c>
-      <c r="U38" t="s">
+      <c r="X38" t="s">
         <v>167</v>
       </c>
-      <c r="V38" t="s">
-        <v>31</v>
-      </c>
-      <c r="W38" t="s">
-        <v>168</v>
-      </c>
-      <c r="X38" t="s">
-        <v>169</v>
-      </c>
       <c r="Y38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
@@ -3631,64 +3610,64 @@
         <v>46148</v>
       </c>
       <c r="B39" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D39" t="s">
+        <v>168</v>
+      </c>
+      <c r="E39" t="s">
+        <v>31</v>
+      </c>
+      <c r="H39" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" t="s">
+        <v>32</v>
+      </c>
+      <c r="K39" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N39" t="s">
+        <v>34</v>
+      </c>
+      <c r="O39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P39" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>34</v>
+      </c>
+      <c r="R39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S39" t="s">
+        <v>161</v>
+      </c>
+      <c r="T39" t="s">
+        <v>169</v>
+      </c>
+      <c r="U39" t="s">
         <v>170</v>
       </c>
-      <c r="E39" t="s">
-        <v>31</v>
-      </c>
-      <c r="H39" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" t="s">
-        <v>32</v>
-      </c>
-      <c r="J39" t="s">
-        <v>32</v>
-      </c>
-      <c r="K39" t="s">
-        <v>32</v>
-      </c>
-      <c r="L39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N39" t="s">
-        <v>34</v>
-      </c>
-      <c r="O39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P39" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>34</v>
-      </c>
-      <c r="R39" t="s">
-        <v>34</v>
-      </c>
-      <c r="S39" t="s">
-        <v>163</v>
-      </c>
-      <c r="T39" t="s">
+      <c r="V39" t="s">
+        <v>31</v>
+      </c>
+      <c r="W39" t="s">
         <v>171</v>
       </c>
-      <c r="U39" t="s">
+      <c r="X39" t="s">
         <v>172</v>
       </c>
-      <c r="V39" t="s">
-        <v>31</v>
-      </c>
-      <c r="W39" t="s">
-        <v>173</v>
-      </c>
-      <c r="X39" t="s">
-        <v>174</v>
-      </c>
       <c r="Y39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
@@ -3696,64 +3675,64 @@
         <v>46148</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
+      </c>
+      <c r="H40" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J40" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" t="s">
+        <v>32</v>
+      </c>
+      <c r="N40" t="s">
+        <v>34</v>
+      </c>
+      <c r="O40" t="s">
+        <v>32</v>
+      </c>
+      <c r="P40" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>34</v>
+      </c>
+      <c r="R40" t="s">
+        <v>34</v>
+      </c>
+      <c r="S40" t="s">
+        <v>174</v>
+      </c>
+      <c r="T40" t="s">
         <v>175</v>
       </c>
-      <c r="E40" t="s">
-        <v>31</v>
-      </c>
-      <c r="H40" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J40" t="s">
-        <v>32</v>
-      </c>
-      <c r="K40" t="s">
-        <v>32</v>
-      </c>
-      <c r="L40" t="s">
-        <v>32</v>
-      </c>
-      <c r="N40" t="s">
-        <v>34</v>
-      </c>
-      <c r="O40" t="s">
-        <v>32</v>
-      </c>
-      <c r="P40" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>34</v>
-      </c>
-      <c r="R40" t="s">
-        <v>34</v>
-      </c>
-      <c r="S40" t="s">
+      <c r="U40" t="s">
         <v>176</v>
       </c>
-      <c r="T40" t="s">
+      <c r="V40" t="s">
+        <v>31</v>
+      </c>
+      <c r="W40" t="s">
         <v>177</v>
       </c>
-      <c r="U40" t="s">
+      <c r="X40" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y40" t="s">
         <v>178</v>
-      </c>
-      <c r="V40" t="s">
-        <v>31</v>
-      </c>
-      <c r="W40" t="s">
-        <v>179</v>
-      </c>
-      <c r="X40" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
@@ -3761,64 +3740,64 @@
         <v>46148</v>
       </c>
       <c r="B41" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" t="s">
+        <v>180</v>
+      </c>
+      <c r="E41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H41" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" t="s">
+        <v>39</v>
+      </c>
+      <c r="J41" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" t="s">
+        <v>32</v>
+      </c>
+      <c r="L41" t="s">
+        <v>32</v>
+      </c>
+      <c r="N41" t="s">
         <v>181</v>
       </c>
-      <c r="D41" t="s">
+      <c r="O41" t="s">
+        <v>32</v>
+      </c>
+      <c r="P41" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>34</v>
+      </c>
+      <c r="R41" t="s">
+        <v>34</v>
+      </c>
+      <c r="S41" t="s">
         <v>182</v>
       </c>
-      <c r="E41" t="s">
-        <v>31</v>
-      </c>
-      <c r="H41" t="s">
-        <v>32</v>
-      </c>
-      <c r="I41" t="s">
-        <v>40</v>
-      </c>
-      <c r="J41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K41" t="s">
-        <v>32</v>
-      </c>
-      <c r="L41" t="s">
-        <v>32</v>
-      </c>
-      <c r="N41" t="s">
+      <c r="T41" t="s">
         <v>183</v>
       </c>
-      <c r="O41" t="s">
-        <v>32</v>
-      </c>
-      <c r="P41" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>34</v>
-      </c>
-      <c r="R41" t="s">
-        <v>34</v>
-      </c>
-      <c r="S41" t="s">
+      <c r="U41" t="s">
         <v>184</v>
       </c>
-      <c r="T41" t="s">
+      <c r="V41" t="s">
+        <v>31</v>
+      </c>
+      <c r="W41" t="s">
         <v>185</v>
       </c>
-      <c r="U41" t="s">
-        <v>186</v>
-      </c>
-      <c r="V41" t="s">
-        <v>31</v>
-      </c>
-      <c r="W41" t="s">
-        <v>187</v>
-      </c>
       <c r="X41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
@@ -3826,10 +3805,10 @@
         <v>46148</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D42" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E42" t="s">
         <v>31</v>
@@ -3862,25 +3841,25 @@
         <v>34</v>
       </c>
       <c r="S42" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="T42" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="U42" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="V42" t="s">
         <v>31</v>
       </c>
       <c r="W42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y42" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
@@ -3888,10 +3867,10 @@
         <v>46149</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E43" t="s">
         <v>31</v>
@@ -3927,19 +3906,19 @@
         <v>34</v>
       </c>
       <c r="S43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T43" t="s">
         <v>34</v>
       </c>
       <c r="W43" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="X43" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Y43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
@@ -3947,10 +3926,10 @@
         <v>46149</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E44" t="s">
         <v>31</v>
@@ -3980,25 +3959,25 @@
         <v>32</v>
       </c>
       <c r="Q44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T44" t="s">
         <v>34</v>
       </c>
       <c r="W44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="X44" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Y44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
@@ -4006,61 +3985,64 @@
         <v>46154</v>
       </c>
       <c r="B45" t="s">
+        <v>204</v>
+      </c>
+      <c r="D45" t="s">
+        <v>189</v>
+      </c>
+      <c r="E45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45" t="s">
+        <v>32</v>
+      </c>
+      <c r="I45" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45" t="s">
+        <v>34</v>
+      </c>
+      <c r="O45" t="s">
+        <v>32</v>
+      </c>
+      <c r="P45" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>34</v>
+      </c>
+      <c r="R45" t="s">
+        <v>34</v>
+      </c>
+      <c r="S45" t="s">
+        <v>135</v>
+      </c>
+      <c r="T45" t="s">
+        <v>126</v>
+      </c>
+      <c r="U45" t="s">
+        <v>190</v>
+      </c>
+      <c r="V45" t="s">
+        <v>31</v>
+      </c>
+      <c r="W45" t="s">
         <v>191</v>
       </c>
-      <c r="D45" t="s">
-        <v>98</v>
-      </c>
-      <c r="E45" t="s">
-        <v>31</v>
-      </c>
-      <c r="H45" t="s">
-        <v>32</v>
-      </c>
-      <c r="I45" t="s">
-        <v>32</v>
-      </c>
-      <c r="J45" t="s">
-        <v>32</v>
-      </c>
-      <c r="K45" t="s">
-        <v>32</v>
-      </c>
-      <c r="L45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N45" t="s">
-        <v>34</v>
-      </c>
-      <c r="O45" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>34</v>
-      </c>
-      <c r="R45" t="s">
-        <v>34</v>
-      </c>
-      <c r="S45" t="s">
-        <v>137</v>
-      </c>
-      <c r="T45" t="s">
+      <c r="X45" t="s">
         <v>192</v>
       </c>
-      <c r="U45" t="s">
+      <c r="Y45" t="s">
         <v>193</v>
-      </c>
-      <c r="V45" t="s">
-        <v>31</v>
-      </c>
-      <c r="W45" t="s">
-        <v>194</v>
-      </c>
-      <c r="X45" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
@@ -4068,49 +4050,49 @@
         <v>46154</v>
       </c>
       <c r="B46" t="s">
+        <v>194</v>
+      </c>
+      <c r="D46" t="s">
         <v>195</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
+        <v>31</v>
+      </c>
+      <c r="H46" t="s">
+        <v>32</v>
+      </c>
+      <c r="I46" t="s">
+        <v>39</v>
+      </c>
+      <c r="J46" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" t="s">
+        <v>32</v>
+      </c>
+      <c r="L46" t="s">
+        <v>32</v>
+      </c>
+      <c r="N46" t="s">
+        <v>34</v>
+      </c>
+      <c r="O46" t="s">
+        <v>32</v>
+      </c>
+      <c r="P46" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>34</v>
+      </c>
+      <c r="R46" t="s">
+        <v>34</v>
+      </c>
+      <c r="S46" t="s">
+        <v>135</v>
+      </c>
+      <c r="T46" t="s">
         <v>196</v>
-      </c>
-      <c r="E46" t="s">
-        <v>31</v>
-      </c>
-      <c r="H46" t="s">
-        <v>32</v>
-      </c>
-      <c r="I46" t="s">
-        <v>32</v>
-      </c>
-      <c r="J46" t="s">
-        <v>32</v>
-      </c>
-      <c r="K46" t="s">
-        <v>32</v>
-      </c>
-      <c r="L46" t="s">
-        <v>32</v>
-      </c>
-      <c r="N46" t="s">
-        <v>34</v>
-      </c>
-      <c r="O46" t="s">
-        <v>32</v>
-      </c>
-      <c r="P46" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>34</v>
-      </c>
-      <c r="R46" t="s">
-        <v>34</v>
-      </c>
-      <c r="S46" t="s">
-        <v>137</v>
-      </c>
-      <c r="T46" t="s">
-        <v>128</v>
       </c>
       <c r="U46" t="s">
         <v>197</v>
@@ -4125,7 +4107,7 @@
         <v>199</v>
       </c>
       <c r="Y46" t="s">
-        <v>200</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
@@ -4133,182 +4115,182 @@
         <v>46154</v>
       </c>
       <c r="B47" t="s">
+        <v>179</v>
+      </c>
+      <c r="D47" t="s">
+        <v>200</v>
+      </c>
+      <c r="E47" t="s">
+        <v>31</v>
+      </c>
+      <c r="H47" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J47" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" t="s">
+        <v>32</v>
+      </c>
+      <c r="L47" t="s">
+        <v>32</v>
+      </c>
+      <c r="N47" t="s">
+        <v>34</v>
+      </c>
+      <c r="O47" t="s">
+        <v>32</v>
+      </c>
+      <c r="P47" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>34</v>
+      </c>
+      <c r="R47" t="s">
+        <v>34</v>
+      </c>
+      <c r="S47" t="s">
+        <v>135</v>
+      </c>
+      <c r="T47" t="s">
         <v>201</v>
       </c>
-      <c r="D47" t="s">
+      <c r="U47" t="s">
         <v>202</v>
       </c>
-      <c r="E47" t="s">
-        <v>31</v>
-      </c>
-      <c r="H47" t="s">
-        <v>32</v>
-      </c>
-      <c r="I47" t="s">
-        <v>40</v>
-      </c>
-      <c r="J47" t="s">
-        <v>32</v>
-      </c>
-      <c r="K47" t="s">
-        <v>32</v>
-      </c>
-      <c r="L47" t="s">
-        <v>32</v>
-      </c>
-      <c r="N47" t="s">
-        <v>34</v>
-      </c>
-      <c r="O47" t="s">
-        <v>32</v>
-      </c>
-      <c r="P47" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>34</v>
-      </c>
-      <c r="R47" t="s">
-        <v>34</v>
-      </c>
-      <c r="S47" t="s">
-        <v>137</v>
-      </c>
-      <c r="T47" t="s">
+      <c r="V47" t="s">
+        <v>31</v>
+      </c>
+      <c r="W47" t="s">
         <v>203</v>
       </c>
-      <c r="U47" t="s">
-        <v>204</v>
-      </c>
-      <c r="V47" t="s">
-        <v>31</v>
-      </c>
-      <c r="W47" t="s">
-        <v>205</v>
-      </c>
       <c r="X47" t="s">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="Y47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B48" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="D48" t="s">
+        <v>205</v>
+      </c>
+      <c r="E48" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48" t="s">
+        <v>206</v>
+      </c>
+      <c r="I48" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" t="s">
+        <v>32</v>
+      </c>
+      <c r="K48" t="s">
+        <v>32</v>
+      </c>
+      <c r="L48" t="s">
+        <v>32</v>
+      </c>
+      <c r="N48" t="s">
+        <v>34</v>
+      </c>
+      <c r="O48" t="s">
+        <v>32</v>
+      </c>
+      <c r="R48" t="s">
+        <v>34</v>
+      </c>
+      <c r="S48" t="s">
         <v>207</v>
       </c>
-      <c r="E48" t="s">
-        <v>31</v>
-      </c>
-      <c r="H48" t="s">
-        <v>32</v>
-      </c>
-      <c r="I48" t="s">
-        <v>32</v>
-      </c>
-      <c r="J48" t="s">
-        <v>32</v>
-      </c>
-      <c r="K48" t="s">
-        <v>32</v>
-      </c>
-      <c r="L48" t="s">
-        <v>32</v>
-      </c>
-      <c r="N48" t="s">
-        <v>34</v>
-      </c>
-      <c r="O48" t="s">
-        <v>32</v>
-      </c>
-      <c r="P48" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>34</v>
-      </c>
-      <c r="R48" t="s">
-        <v>34</v>
-      </c>
-      <c r="S48" t="s">
-        <v>137</v>
-      </c>
       <c r="T48" t="s">
+        <v>34</v>
+      </c>
+      <c r="W48" t="s">
         <v>208</v>
       </c>
-      <c r="U48" t="s">
-        <v>209</v>
-      </c>
-      <c r="V48" t="s">
-        <v>31</v>
-      </c>
-      <c r="W48" t="s">
-        <v>210</v>
-      </c>
       <c r="X48" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="Y48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="B49" t="s">
+        <v>231</v>
+      </c>
+      <c r="D49" t="s">
+        <v>209</v>
+      </c>
+      <c r="E49" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49" t="s">
+        <v>32</v>
+      </c>
+      <c r="I49" t="s">
+        <v>32</v>
+      </c>
+      <c r="J49" t="s">
+        <v>32</v>
+      </c>
+      <c r="K49" t="s">
+        <v>32</v>
+      </c>
+      <c r="L49" t="s">
+        <v>32</v>
+      </c>
+      <c r="N49" t="s">
+        <v>34</v>
+      </c>
+      <c r="O49" t="s">
+        <v>32</v>
+      </c>
+      <c r="P49" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>34</v>
+      </c>
+      <c r="R49" t="s">
+        <v>34</v>
+      </c>
+      <c r="S49" t="s">
+        <v>182</v>
+      </c>
+      <c r="T49" t="s">
+        <v>34</v>
+      </c>
+      <c r="U49" t="s">
+        <v>210</v>
+      </c>
+      <c r="V49" t="s">
+        <v>31</v>
+      </c>
+      <c r="W49" t="s">
+        <v>46</v>
+      </c>
+      <c r="X49" t="s">
         <v>211</v>
       </c>
-      <c r="D49" t="s">
-        <v>212</v>
-      </c>
-      <c r="E49" t="s">
-        <v>31</v>
-      </c>
-      <c r="H49" t="s">
-        <v>213</v>
-      </c>
-      <c r="I49" t="s">
-        <v>32</v>
-      </c>
-      <c r="J49" t="s">
-        <v>32</v>
-      </c>
-      <c r="K49" t="s">
-        <v>32</v>
-      </c>
-      <c r="L49" t="s">
-        <v>32</v>
-      </c>
-      <c r="N49" t="s">
-        <v>34</v>
-      </c>
-      <c r="O49" t="s">
-        <v>32</v>
-      </c>
-      <c r="R49" t="s">
-        <v>34</v>
-      </c>
-      <c r="S49" t="s">
-        <v>214</v>
-      </c>
-      <c r="T49" t="s">
-        <v>34</v>
-      </c>
-      <c r="W49" t="s">
-        <v>215</v>
-      </c>
-      <c r="X49" t="s">
+      <c r="Y49" t="s">
         <v>70</v>
-      </c>
-      <c r="Y49" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.3">
@@ -4316,10 +4298,10 @@
         <v>46161</v>
       </c>
       <c r="B50" t="s">
-        <v>238</v>
+        <v>97</v>
       </c>
       <c r="D50" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E50" t="s">
         <v>31</v>
@@ -4328,7 +4310,7 @@
         <v>32</v>
       </c>
       <c r="I50" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J50" t="s">
         <v>32</v>
@@ -4355,36 +4337,36 @@
         <v>34</v>
       </c>
       <c r="S50" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="T50" t="s">
         <v>34</v>
       </c>
       <c r="U50" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="V50" t="s">
         <v>31</v>
       </c>
       <c r="W50" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="X50" t="s">
-        <v>218</v>
+        <v>99</v>
       </c>
       <c r="Y50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>214</v>
       </c>
       <c r="D51" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="E51" t="s">
         <v>31</v>
@@ -4393,7 +4375,7 @@
         <v>32</v>
       </c>
       <c r="I51" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J51" t="s">
         <v>32</v>
@@ -4420,36 +4402,36 @@
         <v>34</v>
       </c>
       <c r="S51" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="T51" t="s">
-        <v>34</v>
+        <v>215</v>
       </c>
       <c r="U51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V51" t="s">
         <v>31</v>
       </c>
       <c r="W51" t="s">
-        <v>116</v>
+        <v>215</v>
       </c>
       <c r="X51" t="s">
-        <v>100</v>
+        <v>215</v>
       </c>
       <c r="Y51" t="s">
-        <v>71</v>
+        <v>215</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B52" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D52" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="E52" t="s">
         <v>31</v>
@@ -4485,25 +4467,22 @@
         <v>34</v>
       </c>
       <c r="S52" t="s">
-        <v>184</v>
+        <v>55</v>
       </c>
       <c r="T52" t="s">
-        <v>222</v>
-      </c>
-      <c r="U52" t="s">
-        <v>223</v>
+        <v>34</v>
       </c>
       <c r="V52" t="s">
-        <v>31</v>
+        <v>218</v>
       </c>
       <c r="W52" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="X52" t="s">
-        <v>222</v>
+        <v>69</v>
       </c>
       <c r="Y52" t="s">
-        <v>222</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.3">
@@ -4511,11 +4490,11 @@
         <v>46162</v>
       </c>
       <c r="B53" t="s">
+        <v>220</v>
+      </c>
+      <c r="D53" t="s">
         <v>221</v>
       </c>
-      <c r="D53" t="s">
-        <v>224</v>
-      </c>
       <c r="E53" t="s">
         <v>31</v>
       </c>
@@ -4546,73 +4525,91 @@
       <c r="Q53" t="s">
         <v>34</v>
       </c>
-      <c r="R53" t="s">
-        <v>34</v>
-      </c>
-      <c r="S53" t="s">
-        <v>56</v>
-      </c>
       <c r="T53" t="s">
         <v>34</v>
       </c>
       <c r="V53" t="s">
-        <v>225</v>
-      </c>
-      <c r="W53" t="s">
-        <v>226</v>
-      </c>
-      <c r="X53" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B54" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" t="s">
+        <v>212</v>
+      </c>
+      <c r="E54" t="s">
+        <v>31</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G54" t="s">
+        <v>31</v>
+      </c>
+      <c r="H54" t="s">
+        <v>32</v>
+      </c>
+      <c r="I54" t="s">
+        <v>39</v>
+      </c>
+      <c r="J54" t="s">
+        <v>32</v>
+      </c>
+      <c r="K54" t="s">
+        <v>32</v>
+      </c>
+      <c r="L54" t="s">
+        <v>32</v>
+      </c>
+      <c r="M54" t="s">
+        <v>223</v>
+      </c>
+      <c r="N54" t="s">
+        <v>34</v>
+      </c>
+      <c r="O54" t="s">
+        <v>32</v>
+      </c>
+      <c r="P54" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>34</v>
+      </c>
+      <c r="R54" t="s">
+        <v>34</v>
+      </c>
+      <c r="S54" t="s">
+        <v>135</v>
+      </c>
+      <c r="T54" t="s">
+        <v>126</v>
+      </c>
+      <c r="U54" t="s">
+        <v>224</v>
+      </c>
+      <c r="V54" t="s">
+        <v>31</v>
+      </c>
+      <c r="W54" t="s">
+        <v>225</v>
+      </c>
+      <c r="X54" t="s">
+        <v>226</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z54" t="s">
         <v>227</v>
       </c>
-      <c r="D54" t="s">
-        <v>228</v>
-      </c>
-      <c r="E54" t="s">
-        <v>31</v>
-      </c>
-      <c r="H54" t="s">
-        <v>32</v>
-      </c>
-      <c r="I54" t="s">
-        <v>32</v>
-      </c>
-      <c r="J54" t="s">
-        <v>32</v>
-      </c>
-      <c r="K54" t="s">
-        <v>32</v>
-      </c>
-      <c r="L54" t="s">
-        <v>32</v>
-      </c>
-      <c r="N54" t="s">
-        <v>34</v>
-      </c>
-      <c r="O54" t="s">
-        <v>32</v>
-      </c>
-      <c r="P54" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>34</v>
-      </c>
-      <c r="T54" t="s">
-        <v>34</v>
-      </c>
-      <c r="V54" t="s">
-        <v>31</v>
+      <c r="AA54" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.3">
@@ -4620,79 +4617,79 @@
         <v>46163</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="D55" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="E55" t="s">
         <v>31</v>
       </c>
       <c r="F55" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G55" t="s">
+        <v>31</v>
+      </c>
+      <c r="H55" t="s">
+        <v>32</v>
+      </c>
+      <c r="I55" t="s">
+        <v>39</v>
+      </c>
+      <c r="J55" t="s">
+        <v>32</v>
+      </c>
+      <c r="K55" t="s">
+        <v>32</v>
+      </c>
+      <c r="L55" t="s">
+        <v>32</v>
+      </c>
+      <c r="M55" t="s">
+        <v>223</v>
+      </c>
+      <c r="N55" t="s">
+        <v>34</v>
+      </c>
+      <c r="O55" t="s">
+        <v>32</v>
+      </c>
+      <c r="P55" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>34</v>
+      </c>
+      <c r="R55" t="s">
+        <v>34</v>
+      </c>
+      <c r="S55" t="s">
+        <v>135</v>
+      </c>
+      <c r="T55" t="s">
+        <v>126</v>
+      </c>
+      <c r="U55" t="s">
         <v>229</v>
       </c>
-      <c r="G55" t="s">
-        <v>31</v>
-      </c>
-      <c r="H55" t="s">
-        <v>32</v>
-      </c>
-      <c r="I55" t="s">
-        <v>40</v>
-      </c>
-      <c r="J55" t="s">
-        <v>32</v>
-      </c>
-      <c r="K55" t="s">
-        <v>32</v>
-      </c>
-      <c r="L55" t="s">
-        <v>32</v>
-      </c>
-      <c r="M55" t="s">
+      <c r="V55" t="s">
+        <v>31</v>
+      </c>
+      <c r="W55" t="s">
         <v>230</v>
       </c>
-      <c r="N55" t="s">
-        <v>34</v>
-      </c>
-      <c r="O55" t="s">
-        <v>32</v>
-      </c>
-      <c r="P55" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>34</v>
-      </c>
-      <c r="R55" t="s">
-        <v>34</v>
-      </c>
-      <c r="S55" t="s">
-        <v>137</v>
-      </c>
-      <c r="T55" t="s">
-        <v>128</v>
-      </c>
-      <c r="U55" t="s">
-        <v>231</v>
-      </c>
-      <c r="V55" t="s">
-        <v>31</v>
-      </c>
-      <c r="W55" t="s">
-        <v>232</v>
-      </c>
       <c r="X55" t="s">
-        <v>233</v>
+        <v>157</v>
       </c>
       <c r="Y55" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z55" t="s">
-        <v>234</v>
+        <v>27</v>
       </c>
       <c r="AA55" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.3">
@@ -4700,16 +4697,16 @@
         <v>46163</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>231</v>
       </c>
       <c r="D56" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E56" t="s">
         <v>31</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G56" t="s">
         <v>31</v>
@@ -4718,7 +4715,7 @@
         <v>32</v>
       </c>
       <c r="I56" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J56" t="s">
         <v>32</v>
@@ -4730,7 +4727,7 @@
         <v>32</v>
       </c>
       <c r="M56" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N56" t="s">
         <v>34</v>
@@ -4748,48 +4745,48 @@
         <v>34</v>
       </c>
       <c r="S56" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="T56" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="U56" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="V56" t="s">
         <v>31</v>
       </c>
       <c r="W56" t="s">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="X56" t="s">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="Y56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z56" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="AA56" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="B57" t="s">
-        <v>238</v>
+        <v>52</v>
       </c>
       <c r="D57" t="s">
-        <v>216</v>
+        <v>173</v>
       </c>
       <c r="E57" t="s">
         <v>31</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="G57" t="s">
         <v>31</v>
@@ -4810,7 +4807,7 @@
         <v>32</v>
       </c>
       <c r="M57" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N57" t="s">
         <v>34</v>
@@ -4828,31 +4825,31 @@
         <v>34</v>
       </c>
       <c r="S57" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="T57" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="U57" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="V57" t="s">
         <v>31</v>
       </c>
       <c r="W57" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="X57" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="Y57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z57" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AA57" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.3">
@@ -4860,19 +4857,16 @@
         <v>46170</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
-      </c>
-      <c r="C58" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="D58" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E58" t="s">
         <v>31</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G58" t="s">
         <v>31</v>
@@ -4881,7 +4875,7 @@
         <v>32</v>
       </c>
       <c r="I58" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J58" t="s">
         <v>32</v>
@@ -4893,13 +4887,13 @@
         <v>32</v>
       </c>
       <c r="M58" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N58" t="s">
         <v>34</v>
       </c>
       <c r="O58" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P58" t="s">
         <v>32</v>
@@ -4911,31 +4905,31 @@
         <v>34</v>
       </c>
       <c r="S58" t="s">
-        <v>163</v>
+        <v>55</v>
       </c>
       <c r="T58" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="U58" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="V58" t="s">
         <v>31</v>
       </c>
       <c r="W58" t="s">
-        <v>243</v>
+        <v>68</v>
       </c>
       <c r="X58" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="Y58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z58" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AA58" t="s">
-        <v>234</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.3">
@@ -4943,82 +4937,79 @@
         <v>46170</v>
       </c>
       <c r="B59" t="s">
-        <v>161</v>
-      </c>
-      <c r="C59" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="D59" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="E59" t="s">
         <v>31</v>
       </c>
       <c r="F59" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G59" t="s">
+        <v>31</v>
+      </c>
+      <c r="H59" t="s">
+        <v>32</v>
+      </c>
+      <c r="I59" t="s">
+        <v>39</v>
+      </c>
+      <c r="J59" t="s">
+        <v>32</v>
+      </c>
+      <c r="K59" t="s">
+        <v>32</v>
+      </c>
+      <c r="L59" t="s">
+        <v>32</v>
+      </c>
+      <c r="M59" t="s">
+        <v>223</v>
+      </c>
+      <c r="N59" t="s">
+        <v>34</v>
+      </c>
+      <c r="O59" t="s">
+        <v>32</v>
+      </c>
+      <c r="P59" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>34</v>
+      </c>
+      <c r="R59" t="s">
+        <v>34</v>
+      </c>
+      <c r="S59" t="s">
+        <v>55</v>
+      </c>
+      <c r="T59" t="s">
+        <v>126</v>
+      </c>
+      <c r="U59" t="s">
+        <v>244</v>
+      </c>
+      <c r="V59" t="s">
+        <v>31</v>
+      </c>
+      <c r="W59" t="s">
         <v>245</v>
       </c>
-      <c r="G59" t="s">
-        <v>31</v>
-      </c>
-      <c r="H59" t="s">
-        <v>32</v>
-      </c>
-      <c r="I59" t="s">
-        <v>40</v>
-      </c>
-      <c r="J59" t="s">
-        <v>32</v>
-      </c>
-      <c r="K59" t="s">
-        <v>32</v>
-      </c>
-      <c r="L59" t="s">
-        <v>32</v>
-      </c>
-      <c r="M59" t="s">
-        <v>230</v>
-      </c>
-      <c r="N59" t="s">
-        <v>34</v>
-      </c>
-      <c r="O59" t="s">
-        <v>28</v>
-      </c>
-      <c r="P59" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>34</v>
-      </c>
-      <c r="R59" t="s">
-        <v>34</v>
-      </c>
-      <c r="S59" t="s">
-        <v>56</v>
-      </c>
-      <c r="T59" t="s">
-        <v>128</v>
-      </c>
-      <c r="U59" t="s">
-        <v>246</v>
-      </c>
-      <c r="V59" t="s">
-        <v>31</v>
-      </c>
-      <c r="W59" t="s">
-        <v>69</v>
-      </c>
       <c r="X59" t="s">
-        <v>247</v>
+        <v>88</v>
       </c>
       <c r="Y59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z59" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AA59" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.3">
@@ -5026,102 +5017,96 @@
         <v>46170</v>
       </c>
       <c r="B60" t="s">
-        <v>142</v>
-      </c>
-      <c r="C60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" t="s">
+        <v>246</v>
+      </c>
+      <c r="E60" t="s">
+        <v>31</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G60" t="s">
+        <v>31</v>
+      </c>
+      <c r="H60" t="s">
+        <v>32</v>
+      </c>
+      <c r="I60" t="s">
+        <v>32</v>
+      </c>
+      <c r="J60" t="s">
+        <v>32</v>
+      </c>
+      <c r="K60" t="s">
+        <v>32</v>
+      </c>
+      <c r="L60" t="s">
+        <v>32</v>
+      </c>
+      <c r="M60" t="s">
+        <v>223</v>
+      </c>
+      <c r="N60" t="s">
+        <v>34</v>
+      </c>
+      <c r="O60" t="s">
+        <v>28</v>
+      </c>
+      <c r="P60" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>34</v>
+      </c>
+      <c r="R60" t="s">
+        <v>34</v>
+      </c>
+      <c r="S60" t="s">
+        <v>55</v>
+      </c>
+      <c r="T60" t="s">
+        <v>126</v>
+      </c>
+      <c r="U60" t="s">
         <v>248</v>
       </c>
-      <c r="D60" t="s">
-        <v>249</v>
-      </c>
-      <c r="E60" t="s">
-        <v>31</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G60" t="s">
-        <v>31</v>
-      </c>
-      <c r="H60" t="s">
-        <v>32</v>
-      </c>
-      <c r="I60" t="s">
-        <v>40</v>
-      </c>
-      <c r="J60" t="s">
-        <v>32</v>
-      </c>
-      <c r="K60" t="s">
-        <v>32</v>
-      </c>
-      <c r="L60" t="s">
-        <v>32</v>
-      </c>
-      <c r="M60" t="s">
-        <v>230</v>
-      </c>
-      <c r="N60" t="s">
-        <v>34</v>
-      </c>
-      <c r="O60" t="s">
-        <v>32</v>
-      </c>
-      <c r="P60" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>34</v>
-      </c>
-      <c r="R60" t="s">
-        <v>34</v>
-      </c>
-      <c r="S60" t="s">
-        <v>56</v>
-      </c>
-      <c r="T60" t="s">
-        <v>128</v>
-      </c>
-      <c r="U60" t="s">
-        <v>251</v>
-      </c>
       <c r="V60" t="s">
         <v>31</v>
       </c>
       <c r="W60" t="s">
-        <v>252</v>
+        <v>68</v>
       </c>
       <c r="X60" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="Y60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z60" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AA60" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="B61" t="s">
-        <v>50</v>
-      </c>
-      <c r="C61" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D61" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E61" t="s">
         <v>31</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G61" t="s">
         <v>31</v>
@@ -5135,56 +5120,53 @@
       <c r="J61" t="s">
         <v>32</v>
       </c>
-      <c r="K61" t="s">
-        <v>32</v>
-      </c>
       <c r="L61" t="s">
         <v>32</v>
       </c>
       <c r="M61" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N61" t="s">
         <v>34</v>
       </c>
       <c r="O61" t="s">
+        <v>32</v>
+      </c>
+      <c r="P61" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>34</v>
+      </c>
+      <c r="R61" t="s">
+        <v>34</v>
+      </c>
+      <c r="S61" t="s">
+        <v>55</v>
+      </c>
+      <c r="T61" t="s">
+        <v>34</v>
+      </c>
+      <c r="U61" t="s">
+        <v>59</v>
+      </c>
+      <c r="V61" t="s">
         <v>28</v>
       </c>
-      <c r="P61" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>34</v>
-      </c>
-      <c r="R61" t="s">
-        <v>34</v>
-      </c>
-      <c r="S61" t="s">
-        <v>56</v>
-      </c>
-      <c r="T61" t="s">
-        <v>128</v>
-      </c>
-      <c r="U61" t="s">
-        <v>255</v>
-      </c>
-      <c r="V61" t="s">
-        <v>31</v>
-      </c>
       <c r="W61" t="s">
+        <v>98</v>
+      </c>
+      <c r="X61" t="s">
         <v>69</v>
       </c>
-      <c r="X61" t="s">
-        <v>119</v>
-      </c>
       <c r="Y61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z61" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AA61" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.3">
@@ -5192,37 +5174,28 @@
         <v>46182</v>
       </c>
       <c r="B62" t="s">
-        <v>87</v>
-      </c>
-      <c r="C62" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="E62" t="s">
         <v>31</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G62" t="s">
-        <v>31</v>
-      </c>
-      <c r="H62" t="s">
-        <v>32</v>
-      </c>
-      <c r="I62" t="s">
-        <v>32</v>
+        <v>251</v>
       </c>
       <c r="J62" t="s">
         <v>32</v>
       </c>
+      <c r="K62" t="s">
+        <v>32</v>
+      </c>
       <c r="L62" t="s">
         <v>32</v>
       </c>
       <c r="M62" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N62" t="s">
         <v>34</v>
@@ -5240,31 +5213,31 @@
         <v>34</v>
       </c>
       <c r="S62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T62" t="s">
         <v>34</v>
       </c>
       <c r="U62" t="s">
-        <v>60</v>
+        <v>252</v>
       </c>
       <c r="V62" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="W62" t="s">
-        <v>99</v>
+        <v>253</v>
       </c>
       <c r="X62" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y62" t="s">
         <v>70</v>
       </c>
-      <c r="Y62" t="s">
-        <v>71</v>
-      </c>
       <c r="Z62" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AA62" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.3">
@@ -5272,22 +5245,25 @@
         <v>46182</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
-      </c>
-      <c r="C63" t="s">
-        <v>50</v>
+        <v>159</v>
       </c>
       <c r="D63" t="s">
+        <v>254</v>
+      </c>
+      <c r="E63" t="s">
+        <v>31</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="E63" t="s">
-        <v>31</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="J63" t="s">
-        <v>32</v>
+      <c r="G63" t="s">
+        <v>31</v>
+      </c>
+      <c r="H63" t="s">
+        <v>32</v>
+      </c>
+      <c r="I63" t="s">
+        <v>39</v>
       </c>
       <c r="K63" t="s">
         <v>32</v>
@@ -5296,7 +5272,7 @@
         <v>32</v>
       </c>
       <c r="M63" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N63" t="s">
         <v>34</v>
@@ -5304,41 +5280,32 @@
       <c r="O63" t="s">
         <v>32</v>
       </c>
-      <c r="P63" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>34</v>
-      </c>
-      <c r="R63" t="s">
-        <v>34</v>
-      </c>
       <c r="S63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T63" t="s">
         <v>34</v>
       </c>
       <c r="U63" t="s">
-        <v>259</v>
+        <v>59</v>
       </c>
       <c r="V63" t="s">
         <v>31</v>
       </c>
       <c r="W63" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="X63" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="Y63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z63" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AA63" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.3">
@@ -5346,28 +5313,28 @@
         <v>46182</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
-      </c>
-      <c r="C64" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="D64" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E64" t="s">
         <v>31</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="G64" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H64" t="s">
         <v>32</v>
       </c>
       <c r="I64" t="s">
-        <v>40</v>
+        <v>32</v>
+      </c>
+      <c r="J64" t="s">
+        <v>32</v>
       </c>
       <c r="K64" t="s">
         <v>32</v>
@@ -5376,7 +5343,7 @@
         <v>32</v>
       </c>
       <c r="M64" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N64" t="s">
         <v>34</v>
@@ -5384,32 +5351,41 @@
       <c r="O64" t="s">
         <v>32</v>
       </c>
+      <c r="P64" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>34</v>
+      </c>
+      <c r="R64" t="s">
+        <v>34</v>
+      </c>
       <c r="S64" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T64" t="s">
         <v>34</v>
       </c>
       <c r="U64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V64" t="s">
         <v>31</v>
       </c>
       <c r="W64" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="X64" t="s">
-        <v>107</v>
+        <v>259</v>
       </c>
       <c r="Y64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z64" t="s">
-        <v>234</v>
+        <v>27</v>
       </c>
       <c r="AA64" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.3">
@@ -5417,22 +5393,19 @@
         <v>46182</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
-      </c>
-      <c r="C65" t="s">
-        <v>76</v>
+        <v>241</v>
       </c>
       <c r="D65" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E65" t="s">
         <v>31</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G65" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H65" t="s">
         <v>32</v>
@@ -5450,7 +5423,7 @@
         <v>32</v>
       </c>
       <c r="M65" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N65" t="s">
         <v>34</v>
@@ -5468,114 +5441,31 @@
         <v>34</v>
       </c>
       <c r="S65" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="T65" t="s">
         <v>34</v>
       </c>
       <c r="U65" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V65" t="s">
         <v>31</v>
       </c>
       <c r="W65" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="X65" t="s">
-        <v>266</v>
+        <v>88</v>
       </c>
       <c r="Y65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z65" t="s">
         <v>27</v>
       </c>
       <c r="AA65" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A66" s="1">
-        <v>46182</v>
-      </c>
-      <c r="B66" t="s">
-        <v>38</v>
-      </c>
-      <c r="C66" t="s">
-        <v>248</v>
-      </c>
-      <c r="D66" t="s">
-        <v>267</v>
-      </c>
-      <c r="E66" t="s">
-        <v>31</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G66" t="s">
-        <v>31</v>
-      </c>
-      <c r="H66" t="s">
-        <v>32</v>
-      </c>
-      <c r="I66" t="s">
-        <v>32</v>
-      </c>
-      <c r="J66" t="s">
-        <v>32</v>
-      </c>
-      <c r="K66" t="s">
-        <v>32</v>
-      </c>
-      <c r="L66" t="s">
-        <v>32</v>
-      </c>
-      <c r="M66" t="s">
-        <v>230</v>
-      </c>
-      <c r="N66" t="s">
-        <v>34</v>
-      </c>
-      <c r="O66" t="s">
-        <v>32</v>
-      </c>
-      <c r="P66" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>34</v>
-      </c>
-      <c r="R66" t="s">
-        <v>34</v>
-      </c>
-      <c r="S66" t="s">
-        <v>163</v>
-      </c>
-      <c r="T66" t="s">
-        <v>34</v>
-      </c>
-      <c r="U66" t="s">
-        <v>60</v>
-      </c>
-      <c r="V66" t="s">
-        <v>31</v>
-      </c>
-      <c r="W66" t="s">
-        <v>269</v>
-      </c>
-      <c r="X66" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA66" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CHECK LIST - frente de serviço MAIO.xlsx
+++ b/docs/CHECK LIST - frente de serviço MAIO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA0E438-DDBC-4182-B69C-E89CEB37390F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A165575-2011-4410-AE44-DBF7E5E1D7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="270">
   <si>
     <t>DATA </t>
   </si>
@@ -141,6 +141,9 @@
     <t>PGR ;PAE;PLANO DE ABASTECIMENTO DE VEICULOS ;PGRS;MANUAL KIT MITIGAÇÃO ;</t>
   </si>
   <si>
+    <t>Cesar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Conceição </t>
   </si>
   <si>
@@ -351,6 +354,9 @@
     <t>CORDÃO ABSORVENTE ;MANTA ABSORVENTE ;TRAVESSEIRO ABSORVENTE ;PÁ PLASTICA;TURFA ;</t>
   </si>
   <si>
+    <t xml:space="preserve">Jonathan </t>
+  </si>
+  <si>
     <t>PRECISANDO DE MANUTENÇÃO;Sem dispenser de sabão ;</t>
   </si>
   <si>
@@ -592,6 +598,21 @@
   </si>
   <si>
     <t>PAE;PGRS;PLANO DE ABASTECIMENTO DE VEICULOS ;PGR ;CAROMETRO ATUALIZADO;MANUAL KIT MITIGAÇÃO ;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT São Lucas </t>
+  </si>
+  <si>
+    <t>FALTANDO ITENS ;Falta: máscara ;</t>
+  </si>
+  <si>
+    <t>LUVA;OCULOS;MANTA ABSORVENTE ;PÁ PLASTICA;SACO PARA RESIDUOS CONTAMINADOS;CORDÃO ABSORVENTE ;TRAVESSEIRO ABSORVENTE ;TURFA ;FALTA: MÁSCARA ;</t>
+  </si>
+  <si>
+    <t>FDS PRODUTO HDD - MK DL 20;FDS PRODUTO HDD - MK GOMA MG 25 ;FDS PRODUTO HDD - MKGELAL 4500;FDS GASOLINA;FDS CIMENTO ;FALTA A FDS DO SABÃO ;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jhonatan </t>
   </si>
   <si>
     <t xml:space="preserve">CT BARÃO DE ARARIBA </t>
@@ -956,8 +977,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AA65" totalsRowShown="0">
-  <autoFilter ref="A1:AA65" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AA66" totalsRowShown="0">
+  <autoFilter ref="A1:AA66" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="27">
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="DATA " dataDxfId="26"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="EQUIPE " dataDxfId="25"/>
@@ -1288,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA65"/>
+  <dimension ref="A1:AA66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="27" width="20" bestFit="1" customWidth="1"/>
@@ -1438,10 +1459,10 @@
         <v>46118</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>31</v>
@@ -1450,7 +1471,7 @@
         <v>32</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -1477,10 +1498,10 @@
         <v>34</v>
       </c>
       <c r="U3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W3" t="s">
         <v>36</v>
@@ -1489,7 +1510,7 @@
         <v>37</v>
       </c>
       <c r="Y3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
@@ -1497,10 +1518,10 @@
         <v>46118</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>31</v>
@@ -1509,7 +1530,7 @@
         <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J4" t="s">
         <v>32</v>
@@ -1527,7 +1548,7 @@
         <v>32</v>
       </c>
       <c r="Q4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R4" t="s">
         <v>34</v>
@@ -1542,13 +1563,13 @@
         <v>31</v>
       </c>
       <c r="W4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
@@ -1556,10 +1577,10 @@
         <v>46118</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
@@ -1568,7 +1589,7 @@
         <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s">
         <v>32</v>
@@ -1586,7 +1607,7 @@
         <v>32</v>
       </c>
       <c r="Q5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R5" t="s">
         <v>34</v>
@@ -1598,13 +1619,13 @@
         <v>31</v>
       </c>
       <c r="W5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
@@ -1612,10 +1633,10 @@
         <v>46119</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -1624,7 +1645,7 @@
         <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J6" t="s">
         <v>32</v>
@@ -1639,7 +1660,7 @@
         <v>34</v>
       </c>
       <c r="O6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P6" t="s">
         <v>32</v>
@@ -1651,7 +1672,7 @@
         <v>34</v>
       </c>
       <c r="S6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T6" t="s">
         <v>34</v>
@@ -1660,13 +1681,13 @@
         <v>31</v>
       </c>
       <c r="W6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
@@ -1674,10 +1695,10 @@
         <v>46119</v>
       </c>
       <c r="B7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -1686,7 +1707,7 @@
         <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7" t="s">
         <v>32</v>
@@ -1695,7 +1716,7 @@
         <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N7" t="s">
         <v>34</v>
@@ -1707,25 +1728,25 @@
         <v>34</v>
       </c>
       <c r="S7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T7" t="s">
         <v>34</v>
       </c>
       <c r="U7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V7" t="s">
         <v>31</v>
       </c>
       <c r="W7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="X7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
@@ -1733,10 +1754,10 @@
         <v>46119</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>
@@ -1754,7 +1775,7 @@
         <v>32</v>
       </c>
       <c r="L8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N8" t="s">
         <v>34</v>
@@ -1772,22 +1793,22 @@
         <v>34</v>
       </c>
       <c r="S8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T8" t="s">
         <v>34</v>
       </c>
       <c r="U8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Y8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
@@ -1795,10 +1816,10 @@
         <v>46119</v>
       </c>
       <c r="B9" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
         <v>31</v>
@@ -1834,7 +1855,7 @@
         <v>34</v>
       </c>
       <c r="S9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T9" t="s">
         <v>34</v>
@@ -1843,13 +1864,13 @@
         <v>31</v>
       </c>
       <c r="W9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
@@ -1857,61 +1878,61 @@
         <v>46120</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>34</v>
+      </c>
+      <c r="R10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S10" t="s">
+        <v>73</v>
+      </c>
+      <c r="T10" t="s">
+        <v>34</v>
+      </c>
+      <c r="V10" t="s">
+        <v>31</v>
+      </c>
+      <c r="W10" t="s">
+        <v>74</v>
+      </c>
+      <c r="X10" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y10" t="s">
         <v>71</v>
-      </c>
-      <c r="H10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10" t="s">
-        <v>34</v>
-      </c>
-      <c r="O10" t="s">
-        <v>32</v>
-      </c>
-      <c r="P10" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>34</v>
-      </c>
-      <c r="R10" t="s">
-        <v>34</v>
-      </c>
-      <c r="S10" t="s">
-        <v>72</v>
-      </c>
-      <c r="T10" t="s">
-        <v>34</v>
-      </c>
-      <c r="V10" t="s">
-        <v>31</v>
-      </c>
-      <c r="W10" t="s">
-        <v>73</v>
-      </c>
-      <c r="X10" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
@@ -1919,13 +1940,13 @@
         <v>46121</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s">
         <v>32</v>
@@ -1952,28 +1973,28 @@
         <v>32</v>
       </c>
       <c r="Q11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R11" t="s">
         <v>34</v>
       </c>
       <c r="S11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V11" t="s">
         <v>31</v>
       </c>
       <c r="W11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
@@ -1981,10 +2002,10 @@
         <v>46120</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>31</v>
@@ -2011,31 +2032,31 @@
         <v>32</v>
       </c>
       <c r="Q12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R12" t="s">
         <v>34</v>
       </c>
       <c r="S12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T12" t="s">
         <v>34</v>
       </c>
       <c r="U12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V12" t="s">
         <v>31</v>
       </c>
       <c r="W12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
@@ -2043,10 +2064,10 @@
         <v>46120</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -2067,7 +2088,7 @@
         <v>32</v>
       </c>
       <c r="N13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O13" t="s">
         <v>32</v>
@@ -2076,13 +2097,13 @@
         <v>32</v>
       </c>
       <c r="Q13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R13" t="s">
         <v>34</v>
       </c>
       <c r="S13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T13" t="s">
         <v>34</v>
@@ -2091,13 +2112,13 @@
         <v>31</v>
       </c>
       <c r="W13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
@@ -2105,10 +2126,10 @@
         <v>46119</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
@@ -2138,13 +2159,13 @@
         <v>32</v>
       </c>
       <c r="Q14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R14" t="s">
         <v>34</v>
       </c>
       <c r="S14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T14" t="s">
         <v>34</v>
@@ -2153,13 +2174,13 @@
         <v>31</v>
       </c>
       <c r="W14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
@@ -2167,10 +2188,10 @@
         <v>46122</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
@@ -2206,7 +2227,7 @@
         <v>34</v>
       </c>
       <c r="S15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T15" t="s">
         <v>34</v>
@@ -2215,13 +2236,13 @@
         <v>31</v>
       </c>
       <c r="W15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
@@ -2229,10 +2250,10 @@
         <v>46122</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -2262,31 +2283,31 @@
         <v>32</v>
       </c>
       <c r="Q16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R16" t="s">
         <v>34</v>
       </c>
       <c r="S16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T16" t="s">
         <v>34</v>
       </c>
       <c r="U16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V16" t="s">
         <v>31</v>
       </c>
       <c r="W16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
@@ -2294,10 +2315,10 @@
         <v>46122</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s">
         <v>31</v>
@@ -2318,7 +2339,7 @@
         <v>32</v>
       </c>
       <c r="N17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O17" t="s">
         <v>32</v>
@@ -2330,7 +2351,7 @@
         <v>34</v>
       </c>
       <c r="S17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T17" t="s">
         <v>34</v>
@@ -2339,13 +2360,13 @@
         <v>31</v>
       </c>
       <c r="W17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
@@ -2353,10 +2374,10 @@
         <v>46125</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
         <v>31</v>
@@ -2374,7 +2395,7 @@
         <v>32</v>
       </c>
       <c r="L18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N18" t="s">
         <v>34</v>
@@ -2386,13 +2407,13 @@
         <v>32</v>
       </c>
       <c r="Q18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T18" t="s">
         <v>34</v>
@@ -2401,13 +2422,13 @@
         <v>31</v>
       </c>
       <c r="W18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="X18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Y18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
@@ -2415,10 +2436,10 @@
         <v>46126</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
         <v>31</v>
@@ -2436,7 +2457,7 @@
         <v>32</v>
       </c>
       <c r="N19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O19" t="s">
         <v>32</v>
@@ -2454,10 +2475,10 @@
         <v>34</v>
       </c>
       <c r="W19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="X19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -2465,10 +2486,10 @@
         <v>46126</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
         <v>31</v>
@@ -2507,13 +2528,13 @@
         <v>34</v>
       </c>
       <c r="W20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
@@ -2521,10 +2542,10 @@
         <v>46135</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E21" t="s">
         <v>31</v>
@@ -2557,22 +2578,22 @@
         <v>34</v>
       </c>
       <c r="S21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T21" t="s">
         <v>34</v>
       </c>
       <c r="U21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="W21" t="s">
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
@@ -2580,10 +2601,10 @@
         <v>46135</v>
       </c>
       <c r="B22" t="s">
-        <v>204</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E22" t="s">
         <v>31</v>
@@ -2604,7 +2625,7 @@
         <v>32</v>
       </c>
       <c r="N22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O22" t="s">
         <v>32</v>
@@ -2619,7 +2640,7 @@
         <v>34</v>
       </c>
       <c r="S22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T22" t="s">
         <v>34</v>
@@ -2628,13 +2649,13 @@
         <v>31</v>
       </c>
       <c r="W22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="X22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Y22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
@@ -2642,10 +2663,10 @@
         <v>46135</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E23" t="s">
         <v>31</v>
@@ -2681,19 +2702,19 @@
         <v>34</v>
       </c>
       <c r="S23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T23" t="s">
         <v>34</v>
       </c>
       <c r="W23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="X23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
@@ -2701,10 +2722,10 @@
         <v>46135</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E24" t="s">
         <v>31</v>
@@ -2722,10 +2743,10 @@
         <v>32</v>
       </c>
       <c r="L24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O24" t="s">
         <v>32</v>
@@ -2734,19 +2755,19 @@
         <v>34</v>
       </c>
       <c r="S24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T24" t="s">
         <v>34</v>
       </c>
       <c r="W24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="X24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Y24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
@@ -2754,10 +2775,10 @@
         <v>46135</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E25" t="s">
         <v>31</v>
@@ -2778,7 +2799,7 @@
         <v>32</v>
       </c>
       <c r="N25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O25" t="s">
         <v>32</v>
@@ -2793,7 +2814,7 @@
         <v>34</v>
       </c>
       <c r="S25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T25" t="s">
         <v>34</v>
@@ -2802,13 +2823,13 @@
         <v>31</v>
       </c>
       <c r="W25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Y25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
@@ -2816,10 +2837,10 @@
         <v>46139</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s">
         <v>31</v>
@@ -2828,7 +2849,7 @@
         <v>32</v>
       </c>
       <c r="I26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J26" t="s">
         <v>32</v>
@@ -2852,25 +2873,25 @@
         <v>34</v>
       </c>
       <c r="S26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="T26" t="s">
         <v>34</v>
       </c>
       <c r="U26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="V26" t="s">
         <v>31</v>
       </c>
       <c r="W26" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="X26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Y26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
@@ -2878,64 +2899,64 @@
         <v>46139</v>
       </c>
       <c r="B27" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" t="s">
+        <v>40</v>
+      </c>
+      <c r="J27" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" t="s">
+        <v>32</v>
+      </c>
+      <c r="N27" t="s">
+        <v>95</v>
+      </c>
+      <c r="O27" t="s">
+        <v>32</v>
+      </c>
+      <c r="P27" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>34</v>
+      </c>
+      <c r="R27" t="s">
+        <v>34</v>
+      </c>
+      <c r="S27" t="s">
+        <v>127</v>
+      </c>
+      <c r="T27" t="s">
+        <v>128</v>
+      </c>
+      <c r="U27" t="s">
+        <v>129</v>
+      </c>
+      <c r="V27" t="s">
+        <v>31</v>
+      </c>
+      <c r="W27" t="s">
         <v>124</v>
       </c>
-      <c r="D27" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J27" t="s">
-        <v>32</v>
-      </c>
-      <c r="K27" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" t="s">
-        <v>32</v>
-      </c>
-      <c r="N27" t="s">
-        <v>94</v>
-      </c>
-      <c r="O27" t="s">
-        <v>32</v>
-      </c>
-      <c r="P27" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>34</v>
-      </c>
-      <c r="R27" t="s">
-        <v>34</v>
-      </c>
-      <c r="S27" t="s">
+      <c r="X27" t="s">
         <v>125</v>
       </c>
-      <c r="T27" t="s">
-        <v>126</v>
-      </c>
-      <c r="U27" t="s">
-        <v>127</v>
-      </c>
-      <c r="V27" t="s">
-        <v>31</v>
-      </c>
-      <c r="W27" t="s">
-        <v>122</v>
-      </c>
-      <c r="X27" t="s">
-        <v>123</v>
-      </c>
       <c r="Y27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
@@ -2943,16 +2964,16 @@
         <v>46139</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H28" t="s">
         <v>32</v>
       </c>
       <c r="I28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J28" t="s">
         <v>32</v>
@@ -2979,25 +3000,25 @@
         <v>34</v>
       </c>
       <c r="S28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="T28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="U28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="V28" t="s">
         <v>31</v>
       </c>
       <c r="W28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="X28" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Y28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
@@ -3005,10 +3026,10 @@
         <v>46139</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
         <v>31</v>
@@ -3041,25 +3062,25 @@
         <v>34</v>
       </c>
       <c r="S29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T29" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="U29" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="V29" t="s">
         <v>31</v>
       </c>
       <c r="W29" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="X29" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Y29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
@@ -3067,10 +3088,10 @@
         <v>46140</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E30" t="s">
         <v>31</v>
@@ -3097,19 +3118,19 @@
         <v>32</v>
       </c>
       <c r="U30" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="V30" t="s">
         <v>28</v>
       </c>
       <c r="W30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
@@ -3117,10 +3138,10 @@
         <v>46140</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E31" t="s">
         <v>31</v>
@@ -3156,25 +3177,25 @@
         <v>34</v>
       </c>
       <c r="S31" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T31" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="U31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="V31" t="s">
         <v>31</v>
       </c>
       <c r="W31" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="X31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
@@ -3182,10 +3203,10 @@
         <v>46140</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E32" t="s">
         <v>31</v>
@@ -3194,7 +3215,7 @@
         <v>32</v>
       </c>
       <c r="I32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J32" t="s">
         <v>32</v>
@@ -3203,7 +3224,7 @@
         <v>32</v>
       </c>
       <c r="L32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N32" t="s">
         <v>34</v>
@@ -3221,25 +3242,25 @@
         <v>34</v>
       </c>
       <c r="S32" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T32" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="U32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="V32" t="s">
         <v>28</v>
       </c>
       <c r="W32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="X32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Y32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
@@ -3247,10 +3268,10 @@
         <v>46142</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s">
         <v>31</v>
@@ -3286,7 +3307,7 @@
         <v>34</v>
       </c>
       <c r="S33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="T33" t="s">
         <v>34</v>
@@ -3295,13 +3316,13 @@
         <v>31</v>
       </c>
       <c r="W33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="X33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Y33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
@@ -3309,10 +3330,10 @@
         <v>46142</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E34" t="s">
         <v>31</v>
@@ -3342,31 +3363,31 @@
         <v>28</v>
       </c>
       <c r="Q34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R34" t="s">
         <v>34</v>
       </c>
       <c r="S34" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="U34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="V34" t="s">
         <v>31</v>
       </c>
       <c r="W34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X34" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Y34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
@@ -3374,10 +3395,10 @@
         <v>46142</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D35" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E35" t="s">
         <v>31</v>
@@ -3386,7 +3407,7 @@
         <v>32</v>
       </c>
       <c r="I35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J35" t="s">
         <v>32</v>
@@ -3410,19 +3431,19 @@
         <v>34</v>
       </c>
       <c r="S35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V35" t="s">
         <v>31</v>
       </c>
       <c r="W35" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="X35" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Y35" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
@@ -3430,10 +3451,10 @@
         <v>46142</v>
       </c>
       <c r="B36" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E36" t="s">
         <v>31</v>
@@ -3442,7 +3463,7 @@
         <v>32</v>
       </c>
       <c r="I36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J36" t="s">
         <v>32</v>
@@ -3469,7 +3490,7 @@
         <v>34</v>
       </c>
       <c r="S36" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="V36" t="s">
         <v>31</v>
@@ -3480,10 +3501,10 @@
         <v>46147</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E37" t="s">
         <v>31</v>
@@ -3501,7 +3522,7 @@
         <v>32</v>
       </c>
       <c r="L37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N37" t="s">
         <v>34</v>
@@ -3519,25 +3540,25 @@
         <v>34</v>
       </c>
       <c r="S37" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="T37" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="U37" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="V37" t="s">
         <v>31</v>
       </c>
       <c r="W37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="X37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Y37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
@@ -3545,10 +3566,10 @@
         <v>46147</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D38" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E38" t="s">
         <v>31</v>
@@ -3557,7 +3578,7 @@
         <v>32</v>
       </c>
       <c r="I38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J38" t="s">
         <v>32</v>
@@ -3566,7 +3587,7 @@
         <v>32</v>
       </c>
       <c r="L38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N38" t="s">
         <v>34</v>
@@ -3584,25 +3605,25 @@
         <v>34</v>
       </c>
       <c r="S38" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="T38" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="U38" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="V38" t="s">
         <v>31</v>
       </c>
       <c r="W38" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="X38" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Y38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
@@ -3610,10 +3631,10 @@
         <v>46148</v>
       </c>
       <c r="B39" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E39" t="s">
         <v>31</v>
@@ -3649,25 +3670,25 @@
         <v>34</v>
       </c>
       <c r="S39" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="T39" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U39" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="V39" t="s">
         <v>31</v>
       </c>
       <c r="W39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
@@ -3675,10 +3696,10 @@
         <v>46148</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E40" t="s">
         <v>31</v>
@@ -3714,25 +3735,25 @@
         <v>34</v>
       </c>
       <c r="S40" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="T40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="U40" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="V40" t="s">
         <v>31</v>
       </c>
       <c r="W40" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="X40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y40" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
@@ -3740,10 +3761,10 @@
         <v>46148</v>
       </c>
       <c r="B41" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D41" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E41" t="s">
         <v>31</v>
@@ -3752,7 +3773,7 @@
         <v>32</v>
       </c>
       <c r="I41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J41" t="s">
         <v>32</v>
@@ -3764,7 +3785,7 @@
         <v>32</v>
       </c>
       <c r="N41" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O41" t="s">
         <v>32</v>
@@ -3779,25 +3800,25 @@
         <v>34</v>
       </c>
       <c r="S41" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="T41" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="U41" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="V41" t="s">
         <v>31</v>
       </c>
       <c r="W41" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="X41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
@@ -3805,10 +3826,10 @@
         <v>46148</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D42" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E42" t="s">
         <v>31</v>
@@ -3841,25 +3862,25 @@
         <v>34</v>
       </c>
       <c r="S42" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="T42" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="U42" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="V42" t="s">
         <v>31</v>
       </c>
       <c r="W42" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Y42" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
@@ -3867,10 +3888,10 @@
         <v>46149</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D43" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E43" t="s">
         <v>31</v>
@@ -3906,19 +3927,19 @@
         <v>34</v>
       </c>
       <c r="S43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T43" t="s">
         <v>34</v>
       </c>
       <c r="W43" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="X43" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Y43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
@@ -3926,10 +3947,10 @@
         <v>46149</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E44" t="s">
         <v>31</v>
@@ -3959,25 +3980,25 @@
         <v>32</v>
       </c>
       <c r="Q44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T44" t="s">
         <v>34</v>
       </c>
       <c r="W44" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X44" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Y44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
@@ -3985,10 +4006,10 @@
         <v>46154</v>
       </c>
       <c r="B45" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D45" t="s">
-        <v>189</v>
+        <v>98</v>
       </c>
       <c r="E45" t="s">
         <v>31</v>
@@ -4014,9 +4035,6 @@
       <c r="O45" t="s">
         <v>32</v>
       </c>
-      <c r="P45" t="s">
-        <v>32</v>
-      </c>
       <c r="Q45" t="s">
         <v>34</v>
       </c>
@@ -4024,25 +4042,25 @@
         <v>34</v>
       </c>
       <c r="S45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T45" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="U45" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="V45" t="s">
         <v>31</v>
       </c>
       <c r="W45" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="X45" t="s">
-        <v>192</v>
+        <v>100</v>
       </c>
       <c r="Y45" t="s">
-        <v>193</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
@@ -4050,10 +4068,10 @@
         <v>46154</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E46" t="s">
         <v>31</v>
@@ -4062,7 +4080,7 @@
         <v>32</v>
       </c>
       <c r="I46" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J46" t="s">
         <v>32</v>
@@ -4089,10 +4107,10 @@
         <v>34</v>
       </c>
       <c r="S46" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T46" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="U46" t="s">
         <v>197</v>
@@ -4107,7 +4125,7 @@
         <v>199</v>
       </c>
       <c r="Y46" t="s">
-        <v>70</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
@@ -4115,10 +4133,10 @@
         <v>46154</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="D47" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E47" t="s">
         <v>31</v>
@@ -4127,7 +4145,7 @@
         <v>32</v>
       </c>
       <c r="I47" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J47" t="s">
         <v>32</v>
@@ -4154,42 +4172,42 @@
         <v>34</v>
       </c>
       <c r="S47" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T47" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="U47" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="V47" t="s">
         <v>31</v>
       </c>
       <c r="W47" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="X47" t="s">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="Y47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B48" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="D48" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E48" t="s">
         <v>31</v>
       </c>
       <c r="H48" t="s">
-        <v>206</v>
+        <v>32</v>
       </c>
       <c r="I48" t="s">
         <v>32</v>
@@ -4209,40 +4227,52 @@
       <c r="O48" t="s">
         <v>32</v>
       </c>
+      <c r="P48" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>34</v>
+      </c>
       <c r="R48" t="s">
         <v>34</v>
       </c>
       <c r="S48" t="s">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="T48" t="s">
-        <v>34</v>
+        <v>208</v>
+      </c>
+      <c r="U48" t="s">
+        <v>209</v>
+      </c>
+      <c r="V48" t="s">
+        <v>31</v>
       </c>
       <c r="W48" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="X48" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="Y48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B49" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="D49" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E49" t="s">
         <v>31</v>
       </c>
       <c r="H49" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="I49" t="s">
         <v>32</v>
@@ -4262,35 +4292,23 @@
       <c r="O49" t="s">
         <v>32</v>
       </c>
-      <c r="P49" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>34</v>
-      </c>
       <c r="R49" t="s">
         <v>34</v>
       </c>
       <c r="S49" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="T49" t="s">
         <v>34</v>
       </c>
-      <c r="U49" t="s">
-        <v>210</v>
-      </c>
-      <c r="V49" t="s">
-        <v>31</v>
-      </c>
       <c r="W49" t="s">
-        <v>46</v>
+        <v>215</v>
       </c>
       <c r="X49" t="s">
-        <v>211</v>
+        <v>70</v>
       </c>
       <c r="Y49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.3">
@@ -4298,10 +4316,10 @@
         <v>46161</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>238</v>
       </c>
       <c r="D50" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E50" t="s">
         <v>31</v>
@@ -4310,7 +4328,7 @@
         <v>32</v>
       </c>
       <c r="I50" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J50" t="s">
         <v>32</v>
@@ -4337,36 +4355,36 @@
         <v>34</v>
       </c>
       <c r="S50" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="T50" t="s">
         <v>34</v>
       </c>
       <c r="U50" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="V50" t="s">
         <v>31</v>
       </c>
       <c r="W50" t="s">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="X50" t="s">
-        <v>99</v>
+        <v>218</v>
       </c>
       <c r="Y50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B51" t="s">
-        <v>214</v>
+        <v>98</v>
       </c>
       <c r="D51" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="E51" t="s">
         <v>31</v>
@@ -4375,7 +4393,7 @@
         <v>32</v>
       </c>
       <c r="I51" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J51" t="s">
         <v>32</v>
@@ -4402,36 +4420,36 @@
         <v>34</v>
       </c>
       <c r="S51" t="s">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="T51" t="s">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="U51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V51" t="s">
         <v>31</v>
       </c>
       <c r="W51" t="s">
-        <v>215</v>
+        <v>116</v>
       </c>
       <c r="X51" t="s">
-        <v>215</v>
+        <v>100</v>
       </c>
       <c r="Y51" t="s">
-        <v>215</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>46162</v>
+        <v>46168</v>
       </c>
       <c r="B52" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D52" t="s">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="E52" t="s">
         <v>31</v>
@@ -4467,22 +4485,25 @@
         <v>34</v>
       </c>
       <c r="S52" t="s">
-        <v>55</v>
+        <v>184</v>
       </c>
       <c r="T52" t="s">
-        <v>34</v>
+        <v>222</v>
+      </c>
+      <c r="U52" t="s">
+        <v>223</v>
       </c>
       <c r="V52" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="W52" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="X52" t="s">
-        <v>69</v>
+        <v>222</v>
       </c>
       <c r="Y52" t="s">
-        <v>70</v>
+        <v>222</v>
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.3">
@@ -4490,10 +4511,10 @@
         <v>46162</v>
       </c>
       <c r="B53" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D53" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E53" t="s">
         <v>31</v>
@@ -4525,37 +4546,46 @@
       <c r="Q53" t="s">
         <v>34</v>
       </c>
+      <c r="R53" t="s">
+        <v>34</v>
+      </c>
+      <c r="S53" t="s">
+        <v>56</v>
+      </c>
       <c r="T53" t="s">
         <v>34</v>
       </c>
       <c r="V53" t="s">
-        <v>31</v>
+        <v>225</v>
+      </c>
+      <c r="W53" t="s">
+        <v>226</v>
+      </c>
+      <c r="X53" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B54" t="s">
-        <v>112</v>
+        <v>227</v>
       </c>
       <c r="D54" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="E54" t="s">
         <v>31</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="G54" t="s">
-        <v>31</v>
-      </c>
       <c r="H54" t="s">
         <v>32</v>
       </c>
       <c r="I54" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J54" t="s">
         <v>32</v>
@@ -4566,9 +4596,6 @@
       <c r="L54" t="s">
         <v>32</v>
       </c>
-      <c r="M54" t="s">
-        <v>223</v>
-      </c>
       <c r="N54" t="s">
         <v>34</v>
       </c>
@@ -4581,35 +4608,11 @@
       <c r="Q54" t="s">
         <v>34</v>
       </c>
-      <c r="R54" t="s">
-        <v>34</v>
-      </c>
-      <c r="S54" t="s">
-        <v>135</v>
-      </c>
       <c r="T54" t="s">
-        <v>126</v>
-      </c>
-      <c r="U54" t="s">
-        <v>224</v>
+        <v>34</v>
       </c>
       <c r="V54" t="s">
         <v>31</v>
-      </c>
-      <c r="W54" t="s">
-        <v>225</v>
-      </c>
-      <c r="X54" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>227</v>
-      </c>
-      <c r="AA54" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.3">
@@ -4617,16 +4620,16 @@
         <v>46163</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="D55" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E55" t="s">
         <v>31</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G55" t="s">
         <v>31</v>
@@ -4635,7 +4638,7 @@
         <v>32</v>
       </c>
       <c r="I55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J55" t="s">
         <v>32</v>
@@ -4647,7 +4650,7 @@
         <v>32</v>
       </c>
       <c r="M55" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N55" t="s">
         <v>34</v>
@@ -4665,31 +4668,31 @@
         <v>34</v>
       </c>
       <c r="S55" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T55" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="U55" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="V55" t="s">
         <v>31</v>
       </c>
       <c r="W55" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="X55" t="s">
-        <v>157</v>
+        <v>233</v>
       </c>
       <c r="Y55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z55" t="s">
-        <v>27</v>
+        <v>234</v>
       </c>
       <c r="AA55" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.3">
@@ -4697,16 +4700,16 @@
         <v>46163</v>
       </c>
       <c r="B56" t="s">
-        <v>231</v>
+        <v>64</v>
       </c>
       <c r="D56" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E56" t="s">
         <v>31</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G56" t="s">
         <v>31</v>
@@ -4715,7 +4718,7 @@
         <v>32</v>
       </c>
       <c r="I56" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J56" t="s">
         <v>32</v>
@@ -4727,7 +4730,7 @@
         <v>32</v>
       </c>
       <c r="M56" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N56" t="s">
         <v>34</v>
@@ -4745,111 +4748,111 @@
         <v>34</v>
       </c>
       <c r="S56" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="T56" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="U56" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="V56" t="s">
         <v>31</v>
       </c>
       <c r="W56" t="s">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="X56" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="Y56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z56" t="s">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="AA56" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>238</v>
       </c>
       <c r="D57" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="E57" t="s">
         <v>31</v>
       </c>
       <c r="F57" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G57" t="s">
+        <v>31</v>
+      </c>
+      <c r="H57" t="s">
+        <v>32</v>
+      </c>
+      <c r="I57" t="s">
+        <v>32</v>
+      </c>
+      <c r="J57" t="s">
+        <v>32</v>
+      </c>
+      <c r="K57" t="s">
+        <v>32</v>
+      </c>
+      <c r="L57" t="s">
+        <v>32</v>
+      </c>
+      <c r="M57" t="s">
+        <v>230</v>
+      </c>
+      <c r="N57" t="s">
+        <v>34</v>
+      </c>
+      <c r="O57" t="s">
+        <v>32</v>
+      </c>
+      <c r="P57" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>34</v>
+      </c>
+      <c r="R57" t="s">
+        <v>34</v>
+      </c>
+      <c r="S57" t="s">
+        <v>184</v>
+      </c>
+      <c r="T57" t="s">
+        <v>128</v>
+      </c>
+      <c r="U57" t="s">
+        <v>240</v>
+      </c>
+      <c r="V57" t="s">
+        <v>31</v>
+      </c>
+      <c r="W57" t="s">
+        <v>79</v>
+      </c>
+      <c r="X57" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z57" t="s">
         <v>234</v>
       </c>
-      <c r="G57" t="s">
-        <v>31</v>
-      </c>
-      <c r="H57" t="s">
-        <v>32</v>
-      </c>
-      <c r="I57" t="s">
-        <v>32</v>
-      </c>
-      <c r="J57" t="s">
-        <v>32</v>
-      </c>
-      <c r="K57" t="s">
-        <v>32</v>
-      </c>
-      <c r="L57" t="s">
-        <v>32</v>
-      </c>
-      <c r="M57" t="s">
-        <v>223</v>
-      </c>
-      <c r="N57" t="s">
-        <v>34</v>
-      </c>
-      <c r="O57" t="s">
-        <v>32</v>
-      </c>
-      <c r="P57" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>34</v>
-      </c>
-      <c r="R57" t="s">
-        <v>34</v>
-      </c>
-      <c r="S57" t="s">
-        <v>161</v>
-      </c>
-      <c r="T57" t="s">
-        <v>126</v>
-      </c>
-      <c r="U57" t="s">
-        <v>235</v>
-      </c>
-      <c r="V57" t="s">
-        <v>31</v>
-      </c>
-      <c r="W57" t="s">
-        <v>236</v>
-      </c>
-      <c r="X57" t="s">
-        <v>237</v>
-      </c>
-      <c r="Y57" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z57" t="s">
-        <v>227</v>
-      </c>
       <c r="AA57" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.3">
@@ -4857,16 +4860,19 @@
         <v>46170</v>
       </c>
       <c r="B58" t="s">
-        <v>159</v>
+        <v>53</v>
+      </c>
+      <c r="C58" t="s">
+        <v>53</v>
       </c>
       <c r="D58" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E58" t="s">
         <v>31</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G58" t="s">
         <v>31</v>
@@ -4875,7 +4881,7 @@
         <v>32</v>
       </c>
       <c r="I58" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="J58" t="s">
         <v>32</v>
@@ -4887,13 +4893,13 @@
         <v>32</v>
       </c>
       <c r="M58" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N58" t="s">
         <v>34</v>
       </c>
       <c r="O58" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P58" t="s">
         <v>32</v>
@@ -4905,31 +4911,31 @@
         <v>34</v>
       </c>
       <c r="S58" t="s">
-        <v>55</v>
+        <v>163</v>
       </c>
       <c r="T58" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="U58" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="V58" t="s">
         <v>31</v>
       </c>
       <c r="W58" t="s">
-        <v>68</v>
+        <v>243</v>
       </c>
       <c r="X58" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Y58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z58" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AA58" t="s">
-        <v>27</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.3">
@@ -4937,16 +4943,19 @@
         <v>46170</v>
       </c>
       <c r="B59" t="s">
-        <v>140</v>
+        <v>161</v>
+      </c>
+      <c r="C59" t="s">
+        <v>105</v>
       </c>
       <c r="D59" t="s">
-        <v>242</v>
+        <v>175</v>
       </c>
       <c r="E59" t="s">
         <v>31</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G59" t="s">
         <v>31</v>
@@ -4955,7 +4964,7 @@
         <v>32</v>
       </c>
       <c r="I59" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J59" t="s">
         <v>32</v>
@@ -4967,13 +4976,13 @@
         <v>32</v>
       </c>
       <c r="M59" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N59" t="s">
         <v>34</v>
       </c>
       <c r="O59" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P59" t="s">
         <v>32</v>
@@ -4985,31 +4994,31 @@
         <v>34</v>
       </c>
       <c r="S59" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T59" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="U59" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="V59" t="s">
         <v>31</v>
       </c>
       <c r="W59" t="s">
-        <v>245</v>
+        <v>69</v>
       </c>
       <c r="X59" t="s">
-        <v>88</v>
+        <v>247</v>
       </c>
       <c r="Y59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z59" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AA59" t="s">
-        <v>227</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.3">
@@ -5017,16 +5026,19 @@
         <v>46170</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>142</v>
+      </c>
+      <c r="C60" t="s">
+        <v>248</v>
       </c>
       <c r="D60" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E60" t="s">
         <v>31</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G60" t="s">
         <v>31</v>
@@ -5035,7 +5047,7 @@
         <v>32</v>
       </c>
       <c r="I60" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J60" t="s">
         <v>32</v>
@@ -5047,13 +5059,13 @@
         <v>32</v>
       </c>
       <c r="M60" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N60" t="s">
         <v>34</v>
       </c>
       <c r="O60" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P60" t="s">
         <v>32</v>
@@ -5065,48 +5077,51 @@
         <v>34</v>
       </c>
       <c r="S60" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T60" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="U60" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="V60" t="s">
         <v>31</v>
       </c>
       <c r="W60" t="s">
-        <v>68</v>
+        <v>252</v>
       </c>
       <c r="X60" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="Y60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z60" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AA60" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="B61" t="s">
-        <v>86</v>
+        <v>50</v>
+      </c>
+      <c r="C61" t="s">
+        <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E61" t="s">
         <v>31</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G61" t="s">
         <v>31</v>
@@ -5120,17 +5135,20 @@
       <c r="J61" t="s">
         <v>32</v>
       </c>
+      <c r="K61" t="s">
+        <v>32</v>
+      </c>
       <c r="L61" t="s">
         <v>32</v>
       </c>
       <c r="M61" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N61" t="s">
         <v>34</v>
       </c>
       <c r="O61" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P61" t="s">
         <v>32</v>
@@ -5142,31 +5160,31 @@
         <v>34</v>
       </c>
       <c r="S61" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T61" t="s">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="U61" t="s">
-        <v>59</v>
+        <v>255</v>
       </c>
       <c r="V61" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="W61" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="X61" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="Y61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z61" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AA61" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.3">
@@ -5174,28 +5192,37 @@
         <v>46182</v>
       </c>
       <c r="B62" t="s">
-        <v>49</v>
+        <v>87</v>
+      </c>
+      <c r="C62" t="s">
+        <v>87</v>
       </c>
       <c r="D62" t="s">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="E62" t="s">
         <v>31</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
+      </c>
+      <c r="G62" t="s">
+        <v>31</v>
+      </c>
+      <c r="H62" t="s">
+        <v>32</v>
+      </c>
+      <c r="I62" t="s">
+        <v>32</v>
       </c>
       <c r="J62" t="s">
         <v>32</v>
       </c>
-      <c r="K62" t="s">
-        <v>32</v>
-      </c>
       <c r="L62" t="s">
         <v>32</v>
       </c>
       <c r="M62" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N62" t="s">
         <v>34</v>
@@ -5213,31 +5240,31 @@
         <v>34</v>
       </c>
       <c r="S62" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T62" t="s">
         <v>34</v>
       </c>
       <c r="U62" t="s">
-        <v>252</v>
+        <v>60</v>
       </c>
       <c r="V62" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="W62" t="s">
-        <v>253</v>
+        <v>99</v>
       </c>
       <c r="X62" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="Y62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z62" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AA62" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.3">
@@ -5245,25 +5272,22 @@
         <v>46182</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>50</v>
+      </c>
+      <c r="C63" t="s">
+        <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="E63" t="s">
         <v>31</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G63" t="s">
-        <v>31</v>
-      </c>
-      <c r="H63" t="s">
-        <v>32</v>
-      </c>
-      <c r="I63" t="s">
-        <v>39</v>
+        <v>258</v>
+      </c>
+      <c r="J63" t="s">
+        <v>32</v>
       </c>
       <c r="K63" t="s">
         <v>32</v>
@@ -5272,7 +5296,7 @@
         <v>32</v>
       </c>
       <c r="M63" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N63" t="s">
         <v>34</v>
@@ -5280,32 +5304,41 @@
       <c r="O63" t="s">
         <v>32</v>
       </c>
+      <c r="P63" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>34</v>
+      </c>
+      <c r="R63" t="s">
+        <v>34</v>
+      </c>
       <c r="S63" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T63" t="s">
         <v>34</v>
       </c>
       <c r="U63" t="s">
-        <v>59</v>
+        <v>259</v>
       </c>
       <c r="V63" t="s">
         <v>31</v>
       </c>
       <c r="W63" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="X63" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="Y63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z63" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AA63" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.3">
@@ -5313,28 +5346,28 @@
         <v>46182</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>161</v>
+      </c>
+      <c r="C64" t="s">
+        <v>105</v>
       </c>
       <c r="D64" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E64" t="s">
         <v>31</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="G64" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H64" t="s">
         <v>32</v>
       </c>
       <c r="I64" t="s">
-        <v>32</v>
-      </c>
-      <c r="J64" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K64" t="s">
         <v>32</v>
@@ -5343,7 +5376,7 @@
         <v>32</v>
       </c>
       <c r="M64" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N64" t="s">
         <v>34</v>
@@ -5351,41 +5384,32 @@
       <c r="O64" t="s">
         <v>32</v>
       </c>
-      <c r="P64" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>34</v>
-      </c>
-      <c r="R64" t="s">
-        <v>34</v>
-      </c>
       <c r="S64" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T64" t="s">
         <v>34</v>
       </c>
       <c r="U64" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V64" t="s">
         <v>31</v>
       </c>
       <c r="W64" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="X64" t="s">
-        <v>259</v>
+        <v>107</v>
       </c>
       <c r="Y64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z64" t="s">
-        <v>27</v>
+        <v>234</v>
       </c>
       <c r="AA64" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.3">
@@ -5393,19 +5417,22 @@
         <v>46182</v>
       </c>
       <c r="B65" t="s">
-        <v>241</v>
+        <v>76</v>
+      </c>
+      <c r="C65" t="s">
+        <v>76</v>
       </c>
       <c r="D65" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E65" t="s">
         <v>31</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G65" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H65" t="s">
         <v>32</v>
@@ -5423,7 +5450,7 @@
         <v>32</v>
       </c>
       <c r="M65" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="N65" t="s">
         <v>34</v>
@@ -5441,31 +5468,114 @@
         <v>34</v>
       </c>
       <c r="S65" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="T65" t="s">
         <v>34</v>
       </c>
       <c r="U65" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V65" t="s">
         <v>31</v>
       </c>
       <c r="W65" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="X65" t="s">
-        <v>88</v>
+        <v>266</v>
       </c>
       <c r="Y65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z65" t="s">
         <v>27</v>
       </c>
       <c r="AA65" t="s">
-        <v>227</v>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B66" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" t="s">
+        <v>248</v>
+      </c>
+      <c r="D66" t="s">
+        <v>267</v>
+      </c>
+      <c r="E66" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G66" t="s">
+        <v>31</v>
+      </c>
+      <c r="H66" t="s">
+        <v>32</v>
+      </c>
+      <c r="I66" t="s">
+        <v>32</v>
+      </c>
+      <c r="J66" t="s">
+        <v>32</v>
+      </c>
+      <c r="K66" t="s">
+        <v>32</v>
+      </c>
+      <c r="L66" t="s">
+        <v>32</v>
+      </c>
+      <c r="M66" t="s">
+        <v>230</v>
+      </c>
+      <c r="N66" t="s">
+        <v>34</v>
+      </c>
+      <c r="O66" t="s">
+        <v>32</v>
+      </c>
+      <c r="P66" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>34</v>
+      </c>
+      <c r="R66" t="s">
+        <v>34</v>
+      </c>
+      <c r="S66" t="s">
+        <v>163</v>
+      </c>
+      <c r="T66" t="s">
+        <v>34</v>
+      </c>
+      <c r="U66" t="s">
+        <v>60</v>
+      </c>
+      <c r="V66" t="s">
+        <v>31</v>
+      </c>
+      <c r="W66" t="s">
+        <v>269</v>
+      </c>
+      <c r="X66" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>
